--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125502458</v>
+        <v>125500887</v>
       </c>
       <c r="B2" t="n">
-        <v>58111</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600004</v>
+        <v>600005</v>
       </c>
       <c r="R2" t="n">
-        <v>7054538</v>
+        <v>7054287</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125500887</v>
+        <v>125500716</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>58001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,20 +804,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -827,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600005</v>
+        <v>600025</v>
       </c>
       <c r="R3" t="n">
-        <v>7054287</v>
+        <v>7054340</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125499915</v>
+        <v>125500211</v>
       </c>
       <c r="B4" t="n">
         <v>80028</v>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600067</v>
+        <v>600028</v>
       </c>
       <c r="R4" t="n">
-        <v>7054367</v>
+        <v>7054350</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125500946</v>
+        <v>125499915</v>
       </c>
       <c r="B5" t="n">
         <v>80028</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600005</v>
+        <v>600067</v>
       </c>
       <c r="R5" t="n">
-        <v>7054287</v>
+        <v>7054367</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125500716</v>
+        <v>125502458</v>
       </c>
       <c r="B6" t="n">
-        <v>58001</v>
+        <v>58111</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600025</v>
+        <v>600004</v>
       </c>
       <c r="R6" t="n">
-        <v>7054340</v>
+        <v>7054538</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1352,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125500211</v>
+        <v>125500946</v>
       </c>
       <c r="B8" t="n">
         <v>80028</v>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600028</v>
+        <v>600005</v>
       </c>
       <c r="R8" t="n">
-        <v>7054350</v>
+        <v>7054287</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,6 +1461,2702 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125539229</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91116</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>112</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>600039</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7054564</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125539241</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96395</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>600037</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7054531</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125539222</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>600042</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7054425</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125546824</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80056</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lövsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>600048</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7054324</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125547007</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58111</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lövsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>600031</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7054500</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125539228</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91116</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>112</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>600053</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7054518</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125539223</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>600053</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7054518</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125539232</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>600113</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7054480</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125546798</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98290</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lövsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>600057</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7054319</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125539237</v>
+      </c>
+      <c r="B18" t="n">
+        <v>82737</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>600033</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7054517</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125539234</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>600103</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7054444</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125546783</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lövsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>600045</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7054287</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125546946</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lövsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>600111</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7054404</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125539233</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>600112</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7054472</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125539230</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91459</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>658</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>600030</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7054566</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125539219</v>
+      </c>
+      <c r="B24" t="n">
+        <v>75025</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>600032</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7054519</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125539224</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>600042</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7054542</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125539225</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>600039</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7054564</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125539231</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>600070</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7054545</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125539226</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>600033</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7054530</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gammalt bohål 1,5m upp i död gran. 4-4.5cm diameter</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125539220</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91131</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>600070</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7054542</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125539227</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80057</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>600060</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7054552</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125539235</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>600048</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7054427</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125539238</v>
+      </c>
+      <c r="B32" t="n">
+        <v>82737</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>600058</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7054532</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125539239</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92448</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>599889</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7054625</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125546864</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lövsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>600102</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7054399</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125500716</v>
+        <v>125500211</v>
       </c>
       <c r="B3" t="n">
-        <v>58001</v>
+        <v>80028</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600025</v>
+        <v>600028</v>
       </c>
       <c r="R3" t="n">
-        <v>7054340</v>
+        <v>7054350</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125500211</v>
+        <v>125500716</v>
       </c>
       <c r="B4" t="n">
-        <v>80028</v>
+        <v>58001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600028</v>
+        <v>600025</v>
       </c>
       <c r="R4" t="n">
-        <v>7054350</v>
+        <v>7054340</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125539229</v>
+        <v>125539241</v>
       </c>
       <c r="B9" t="n">
-        <v>91116</v>
+        <v>96395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1476,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600039</v>
+        <v>600037</v>
       </c>
       <c r="R9" t="n">
-        <v>7054564</v>
+        <v>7054531</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125539241</v>
+        <v>125539229</v>
       </c>
       <c r="B10" t="n">
-        <v>96395</v>
+        <v>91116</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,25 +1578,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600037</v>
+        <v>600039</v>
       </c>
       <c r="R10" t="n">
-        <v>7054531</v>
+        <v>7054564</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125539220</v>
+        <v>125539227</v>
       </c>
       <c r="B29" t="n">
-        <v>91131</v>
+        <v>80057</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3560,21 +3560,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>600070</v>
+        <v>600060</v>
       </c>
       <c r="R29" t="n">
-        <v>7054542</v>
+        <v>7054552</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3646,10 +3646,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125539227</v>
+        <v>125539220</v>
       </c>
       <c r="B30" t="n">
-        <v>80057</v>
+        <v>91131</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>600060</v>
+        <v>600070</v>
       </c>
       <c r="R30" t="n">
-        <v>7054552</v>
+        <v>7054542</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125500887</v>
+        <v>125500946</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,7 +721,7 @@
         <v>7054287</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125500211</v>
+        <v>125499358</v>
       </c>
       <c r="B3" t="n">
-        <v>80028</v>
+        <v>97147</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600028</v>
+        <v>600146</v>
       </c>
       <c r="R3" t="n">
-        <v>7054350</v>
+        <v>7054420</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125500716</v>
+        <v>125502458</v>
       </c>
       <c r="B4" t="n">
-        <v>58001</v>
+        <v>58111</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600025</v>
+        <v>600004</v>
       </c>
       <c r="R4" t="n">
-        <v>7054340</v>
+        <v>7054538</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125499915</v>
+        <v>125500872</v>
       </c>
       <c r="B5" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600067</v>
+        <v>600005</v>
       </c>
       <c r="R5" t="n">
-        <v>7054367</v>
+        <v>7054287</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125502458</v>
+        <v>125499915</v>
       </c>
       <c r="B6" t="n">
-        <v>58111</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600004</v>
+        <v>600067</v>
       </c>
       <c r="R6" t="n">
-        <v>7054538</v>
+        <v>7054367</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125499358</v>
+        <v>125500211</v>
       </c>
       <c r="B7" t="n">
-        <v>97147</v>
+        <v>80028</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,25 +1252,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600146</v>
+        <v>600028</v>
       </c>
       <c r="R7" t="n">
-        <v>7054420</v>
+        <v>7054350</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125500946</v>
+        <v>125500716</v>
       </c>
       <c r="B8" t="n">
-        <v>80028</v>
+        <v>58001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,25 +1364,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600005</v>
+        <v>600025</v>
       </c>
       <c r="R8" t="n">
-        <v>7054287</v>
+        <v>7054340</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125539241</v>
+        <v>125539223</v>
       </c>
       <c r="B9" t="n">
-        <v>96395</v>
+        <v>91166</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1476,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600037</v>
+        <v>600053</v>
       </c>
       <c r="R9" t="n">
-        <v>7054531</v>
+        <v>7054518</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125539229</v>
+        <v>125539226</v>
       </c>
       <c r="B10" t="n">
-        <v>91116</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,34 +1582,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600039</v>
+        <v>600033</v>
       </c>
       <c r="R10" t="n">
-        <v>7054564</v>
+        <v>7054530</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1642,6 +1647,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammalt bohål 1,5m upp i död gran. 4-4.5cm diameter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125539222</v>
+        <v>125546798</v>
       </c>
       <c r="B11" t="n">
-        <v>91166</v>
+        <v>98290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,41 +1690,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600042</v>
+        <v>600057</v>
       </c>
       <c r="R11" t="n">
-        <v>7054425</v>
+        <v>7054319</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,28 +1766,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125546824</v>
+        <v>125539241</v>
       </c>
       <c r="B12" t="n">
-        <v>80056</v>
+        <v>96395</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,40 +1801,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600048</v>
+        <v>600037</v>
       </c>
       <c r="R12" t="n">
-        <v>7054324</v>
+        <v>7054531</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,29 +1869,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125547007</v>
+        <v>125546864</v>
       </c>
       <c r="B13" t="n">
-        <v>58111</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,31 +1903,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1924,10 +1930,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600031</v>
+        <v>600102</v>
       </c>
       <c r="R13" t="n">
-        <v>7054500</v>
+        <v>7054399</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,6 +1974,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1986,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125539228</v>
+        <v>125539230</v>
       </c>
       <c r="B14" t="n">
-        <v>91116</v>
+        <v>91459</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2002,21 +2009,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2026,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600053</v>
+        <v>600030</v>
       </c>
       <c r="R14" t="n">
-        <v>7054518</v>
+        <v>7054566</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2088,7 +2095,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125539223</v>
+        <v>125539225</v>
       </c>
       <c r="B15" t="n">
         <v>91166</v>
@@ -2128,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600053</v>
+        <v>600039</v>
       </c>
       <c r="R15" t="n">
-        <v>7054518</v>
+        <v>7054564</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2190,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125539232</v>
+        <v>125539222</v>
       </c>
       <c r="B16" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2206,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600113</v>
+        <v>600042</v>
       </c>
       <c r="R16" t="n">
-        <v>7054480</v>
+        <v>7054425</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2292,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125546798</v>
+        <v>125539234</v>
       </c>
       <c r="B17" t="n">
-        <v>98290</v>
+        <v>80028</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2304,45 +2311,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600057</v>
+        <v>600103</v>
       </c>
       <c r="R17" t="n">
-        <v>7054319</v>
+        <v>7054444</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2380,29 +2383,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125539237</v>
+        <v>125546824</v>
       </c>
       <c r="B18" t="n">
-        <v>82737</v>
+        <v>80056</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,41 +2413,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600033</v>
+        <v>600048</v>
       </c>
       <c r="R18" t="n">
-        <v>7054517</v>
+        <v>7054324</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2483,28 +2488,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125539234</v>
+        <v>125546783</v>
       </c>
       <c r="B19" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2517,37 +2523,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600103</v>
+        <v>600045</v>
       </c>
       <c r="R19" t="n">
-        <v>7054444</v>
+        <v>7054287</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2585,28 +2594,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125546783</v>
+        <v>125539224</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2619,40 +2629,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600045</v>
+        <v>600042</v>
       </c>
       <c r="R20" t="n">
-        <v>7054287</v>
+        <v>7054542</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2690,29 +2697,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125546946</v>
+        <v>125539231</v>
       </c>
       <c r="B21" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2725,41 +2731,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600111</v>
+        <v>600070</v>
       </c>
       <c r="R21" t="n">
-        <v>7054404</v>
+        <v>7054545</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2789,11 +2791,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2808,22 +2805,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125539233</v>
+        <v>125539227</v>
       </c>
       <c r="B22" t="n">
-        <v>80028</v>
+        <v>80057</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,25 +2829,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2857,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600112</v>
+        <v>600060</v>
       </c>
       <c r="R22" t="n">
-        <v>7054472</v>
+        <v>7054552</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2922,10 +2919,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125539230</v>
+        <v>125547007</v>
       </c>
       <c r="B23" t="n">
-        <v>91459</v>
+        <v>58111</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,37 +2935,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>103018</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600030</v>
+        <v>600031</v>
       </c>
       <c r="R23" t="n">
-        <v>7054566</v>
+        <v>7054500</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3012,22 +3017,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125539219</v>
+        <v>125539233</v>
       </c>
       <c r="B24" t="n">
-        <v>75025</v>
+        <v>80028</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3040,21 +3045,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600032</v>
+        <v>600112</v>
       </c>
       <c r="R24" t="n">
-        <v>7054519</v>
+        <v>7054472</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3126,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125539224</v>
+        <v>125539220</v>
       </c>
       <c r="B25" t="n">
-        <v>91166</v>
+        <v>91131</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3138,25 +3143,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,7 +3171,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600042</v>
+        <v>600070</v>
       </c>
       <c r="R25" t="n">
         <v>7054542</v>
@@ -3228,10 +3233,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125539225</v>
+        <v>125539238</v>
       </c>
       <c r="B26" t="n">
-        <v>91166</v>
+        <v>82737</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3249,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600039</v>
+        <v>600058</v>
       </c>
       <c r="R26" t="n">
-        <v>7054564</v>
+        <v>7054532</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3330,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125539231</v>
+        <v>125539219</v>
       </c>
       <c r="B27" t="n">
-        <v>80028</v>
+        <v>75025</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3346,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600070</v>
+        <v>600032</v>
       </c>
       <c r="R27" t="n">
-        <v>7054545</v>
+        <v>7054519</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3432,10 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125539226</v>
+        <v>125539232</v>
       </c>
       <c r="B28" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3448,39 +3453,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600033</v>
+        <v>600113</v>
       </c>
       <c r="R28" t="n">
-        <v>7054530</v>
+        <v>7054480</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3513,11 +3513,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gammalt bohål 1,5m upp i död gran. 4-4.5cm diameter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125539227</v>
+        <v>125546946</v>
       </c>
       <c r="B29" t="n">
-        <v>80057</v>
+        <v>57635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3556,41 +3551,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>600060</v>
+        <v>600111</v>
       </c>
       <c r="R29" t="n">
-        <v>7054552</v>
+        <v>7054404</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3620,6 +3619,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3634,22 +3638,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125539220</v>
+        <v>125539235</v>
       </c>
       <c r="B30" t="n">
-        <v>91131</v>
+        <v>80028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3658,25 +3662,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3686,10 +3690,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>600070</v>
+        <v>600048</v>
       </c>
       <c r="R30" t="n">
-        <v>7054542</v>
+        <v>7054427</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3748,10 +3752,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125539235</v>
+        <v>125539228</v>
       </c>
       <c r="B31" t="n">
-        <v>80028</v>
+        <v>91116</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3764,21 +3768,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3792,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>600048</v>
+        <v>600053</v>
       </c>
       <c r="R31" t="n">
-        <v>7054427</v>
+        <v>7054518</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3850,10 +3854,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125539238</v>
+        <v>125539239</v>
       </c>
       <c r="B32" t="n">
-        <v>82737</v>
+        <v>92448</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3862,25 +3866,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3890,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>600058</v>
+        <v>599889</v>
       </c>
       <c r="R32" t="n">
-        <v>7054532</v>
+        <v>7054625</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3952,10 +3956,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125539239</v>
+        <v>125539237</v>
       </c>
       <c r="B33" t="n">
-        <v>92448</v>
+        <v>82737</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3964,25 +3968,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +3996,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599889</v>
+        <v>600033</v>
       </c>
       <c r="R33" t="n">
-        <v>7054625</v>
+        <v>7054517</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4054,10 +4058,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125546864</v>
+        <v>125539229</v>
       </c>
       <c r="B34" t="n">
-        <v>78947</v>
+        <v>91116</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4070,40 +4074,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>600102</v>
+        <v>600039</v>
       </c>
       <c r="R34" t="n">
-        <v>7054399</v>
+        <v>7054564</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4141,19 +4142,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -3650,10 +3650,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125539235</v>
+        <v>125539228</v>
       </c>
       <c r="B30" t="n">
-        <v>80028</v>
+        <v>91116</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>600048</v>
+        <v>600053</v>
       </c>
       <c r="R30" t="n">
-        <v>7054427</v>
+        <v>7054518</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3752,10 +3752,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125539228</v>
+        <v>125539239</v>
       </c>
       <c r="B31" t="n">
-        <v>91116</v>
+        <v>92448</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3764,25 +3764,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>600053</v>
+        <v>599889</v>
       </c>
       <c r="R31" t="n">
-        <v>7054518</v>
+        <v>7054625</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3854,10 +3854,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125539239</v>
+        <v>125539235</v>
       </c>
       <c r="B32" t="n">
-        <v>92448</v>
+        <v>80028</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3866,25 +3866,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599889</v>
+        <v>600048</v>
       </c>
       <c r="R32" t="n">
-        <v>7054625</v>
+        <v>7054427</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -2919,10 +2919,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125547007</v>
+        <v>125539233</v>
       </c>
       <c r="B23" t="n">
-        <v>58111</v>
+        <v>80028</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2935,45 +2935,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103018</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600031</v>
+        <v>600112</v>
       </c>
       <c r="R23" t="n">
-        <v>7054500</v>
+        <v>7054472</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3017,22 +3009,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125539233</v>
+        <v>125539220</v>
       </c>
       <c r="B24" t="n">
-        <v>80028</v>
+        <v>91131</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3041,25 +3033,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3069,10 +3061,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600112</v>
+        <v>600070</v>
       </c>
       <c r="R24" t="n">
-        <v>7054472</v>
+        <v>7054542</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3131,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125539220</v>
+        <v>125547007</v>
       </c>
       <c r="B25" t="n">
-        <v>91131</v>
+        <v>58111</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3143,41 +3135,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>103018</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600070</v>
+        <v>600031</v>
       </c>
       <c r="R25" t="n">
-        <v>7054542</v>
+        <v>7054500</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3221,12 +3221,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125500946</v>
+        <v>125500872</v>
       </c>
       <c r="B2" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,7 +716,7 @@
         <v>7054287</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125499358</v>
+        <v>125500946</v>
       </c>
       <c r="B3" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600146</v>
+        <v>600005</v>
       </c>
       <c r="R3" t="n">
-        <v>7054420</v>
+        <v>7054287</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125502458</v>
+        <v>125499915</v>
       </c>
       <c r="B4" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600004</v>
+        <v>600067</v>
       </c>
       <c r="R4" t="n">
-        <v>7054538</v>
+        <v>7054367</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,32 +1001,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125500872</v>
+        <v>125500716</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1051,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600005</v>
+        <v>600025</v>
       </c>
       <c r="R5" t="n">
-        <v>7054287</v>
+        <v>7054340</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,15 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125499915</v>
+        <v>125500211</v>
       </c>
       <c r="B6" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600067</v>
+        <v>600028</v>
       </c>
       <c r="R6" t="n">
-        <v>7054367</v>
+        <v>7054350</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1203,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,37 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125500211</v>
+        <v>125499358</v>
       </c>
       <c r="B7" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,13 +1250,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600028</v>
+        <v>600146</v>
       </c>
       <c r="R7" t="n">
-        <v>7054350</v>
+        <v>7054420</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,37 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125500716</v>
+        <v>125502458</v>
       </c>
       <c r="B8" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,13 +1357,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600025</v>
+        <v>600004</v>
       </c>
       <c r="R8" t="n">
-        <v>7054340</v>
+        <v>7054538</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,15 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125539223</v>
+        <v>125539229</v>
       </c>
       <c r="B9" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91170</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600053</v>
+        <v>600039</v>
       </c>
       <c r="R9" t="n">
-        <v>7054518</v>
+        <v>7054564</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1566,55 +1526,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125539226</v>
+        <v>125539239</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600033</v>
+        <v>599889</v>
       </c>
       <c r="R10" t="n">
-        <v>7054530</v>
+        <v>7054625</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1647,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gammalt bohål 1,5m upp i död gran. 4-4.5cm diameter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,57 +1623,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125546798</v>
+        <v>125539231</v>
       </c>
       <c r="B11" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600057</v>
+        <v>600070</v>
       </c>
       <c r="R11" t="n">
-        <v>7054319</v>
+        <v>7054545</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1766,34 +1702,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125539241</v>
+        <v>125546798</v>
       </c>
       <c r="B12" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,37 +1731,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600037</v>
+        <v>600057</v>
       </c>
       <c r="R12" t="n">
-        <v>7054531</v>
+        <v>7054319</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1869,33 +1803,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125546864</v>
+        <v>125546946</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,26 +1833,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1930,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600102</v>
+        <v>600111</v>
       </c>
       <c r="R13" t="n">
-        <v>7054399</v>
+        <v>7054404</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,13 +1899,17 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1993,15 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125539230</v>
+        <v>125539228</v>
       </c>
       <c r="B14" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91170</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,21 +1939,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2033,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600030</v>
+        <v>600053</v>
       </c>
       <c r="R14" t="n">
-        <v>7054566</v>
+        <v>7054518</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2095,15 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125539225</v>
+        <v>125539238</v>
       </c>
       <c r="B15" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,21 +2036,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2135,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600039</v>
+        <v>600058</v>
       </c>
       <c r="R15" t="n">
-        <v>7054564</v>
+        <v>7054532</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2197,15 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125539222</v>
+        <v>125546783</v>
       </c>
       <c r="B16" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,37 +2133,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600042</v>
+        <v>600045</v>
       </c>
       <c r="R16" t="n">
-        <v>7054425</v>
+        <v>7054287</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,33 +2204,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125539234</v>
+        <v>125539226</v>
       </c>
       <c r="B17" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,34 +2234,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600103</v>
+        <v>600033</v>
       </c>
       <c r="R17" t="n">
-        <v>7054444</v>
+        <v>7054530</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2375,6 +2299,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gammalt bohål 1,5m upp i död gran. 4-4.5cm diameter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,56 +2330,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125546824</v>
+        <v>125539232</v>
       </c>
       <c r="B18" t="n">
-        <v>80056</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600048</v>
+        <v>600113</v>
       </c>
       <c r="R18" t="n">
-        <v>7054324</v>
+        <v>7054480</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2488,56 +2409,50 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125546783</v>
+        <v>125546824</v>
       </c>
       <c r="B19" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80098</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2550,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600045</v>
+        <v>600048</v>
       </c>
       <c r="R19" t="n">
-        <v>7054287</v>
+        <v>7054324</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2613,15 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125539224</v>
+        <v>125539234</v>
       </c>
       <c r="B20" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2629,21 +2539,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2653,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600042</v>
+        <v>600103</v>
       </c>
       <c r="R20" t="n">
-        <v>7054542</v>
+        <v>7054444</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2715,37 +2625,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125539231</v>
+        <v>125539241</v>
       </c>
       <c r="B21" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2755,10 +2660,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600070</v>
+        <v>600037</v>
       </c>
       <c r="R21" t="n">
-        <v>7054545</v>
+        <v>7054531</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2817,37 +2722,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125539227</v>
+        <v>125539225</v>
       </c>
       <c r="B22" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2857,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600060</v>
+        <v>600039</v>
       </c>
       <c r="R22" t="n">
-        <v>7054552</v>
+        <v>7054564</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2919,15 +2819,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125539233</v>
+        <v>125539235</v>
       </c>
       <c r="B23" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,10 +2854,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600112</v>
+        <v>600048</v>
       </c>
       <c r="R23" t="n">
-        <v>7054472</v>
+        <v>7054427</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3021,37 +2916,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125539220</v>
+        <v>125539230</v>
       </c>
       <c r="B24" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3061,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600070</v>
+        <v>600030</v>
       </c>
       <c r="R24" t="n">
-        <v>7054542</v>
+        <v>7054566</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3123,61 +3013,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125547007</v>
+        <v>125539227</v>
       </c>
       <c r="B25" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103018</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600031</v>
+        <v>600060</v>
       </c>
       <c r="R25" t="n">
-        <v>7054500</v>
+        <v>7054552</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3221,27 +3098,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125539238</v>
+        <v>125539222</v>
       </c>
       <c r="B26" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,21 +3121,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3273,10 +3145,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600058</v>
+        <v>600042</v>
       </c>
       <c r="R26" t="n">
-        <v>7054532</v>
+        <v>7054425</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3335,15 +3207,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125539219</v>
+        <v>125539223</v>
       </c>
       <c r="B27" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3351,21 +3218,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3242,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600032</v>
+        <v>600053</v>
       </c>
       <c r="R27" t="n">
-        <v>7054519</v>
+        <v>7054518</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3437,15 +3304,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125539232</v>
+        <v>125539224</v>
       </c>
       <c r="B28" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3453,21 +3315,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3477,10 +3339,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600113</v>
+        <v>600042</v>
       </c>
       <c r="R28" t="n">
-        <v>7054480</v>
+        <v>7054542</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3539,15 +3401,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125546946</v>
+        <v>125539219</v>
       </c>
       <c r="B29" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75066</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3555,41 +3412,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>600111</v>
+        <v>600032</v>
       </c>
       <c r="R29" t="n">
-        <v>7054404</v>
+        <v>7054519</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3619,11 +3472,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ringhack gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3638,27 +3486,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125539228</v>
+        <v>125539233</v>
       </c>
       <c r="B30" t="n">
-        <v>91116</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3666,21 +3509,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3690,10 +3533,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>600053</v>
+        <v>600112</v>
       </c>
       <c r="R30" t="n">
-        <v>7054518</v>
+        <v>7054472</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3752,53 +3595,56 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125539239</v>
+        <v>125547007</v>
       </c>
       <c r="B31" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>103018</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599889</v>
+        <v>600031</v>
       </c>
       <c r="R31" t="n">
-        <v>7054625</v>
+        <v>7054500</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3842,49 +3688,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125539235</v>
+        <v>125539220</v>
       </c>
       <c r="B32" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3894,10 +3735,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>600048</v>
+        <v>600070</v>
       </c>
       <c r="R32" t="n">
-        <v>7054427</v>
+        <v>7054542</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3959,12 +3800,7 @@
         <v>125539237</v>
       </c>
       <c r="B33" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4058,15 +3894,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125539229</v>
+        <v>125546864</v>
       </c>
       <c r="B34" t="n">
-        <v>91116</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4074,37 +3905,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>600039</v>
+        <v>600102</v>
       </c>
       <c r="R34" t="n">
-        <v>7054564</v>
+        <v>7054399</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4142,18 +3976,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -2819,10 +2819,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125539235</v>
+        <v>125539230</v>
       </c>
       <c r="B23" t="n">
-        <v>80070</v>
+        <v>91513</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600048</v>
+        <v>600030</v>
       </c>
       <c r="R23" t="n">
-        <v>7054427</v>
+        <v>7054566</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125539230</v>
+        <v>125539235</v>
       </c>
       <c r="B24" t="n">
-        <v>91513</v>
+        <v>80070</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2927,21 +2927,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600030</v>
+        <v>600048</v>
       </c>
       <c r="R24" t="n">
-        <v>7054566</v>
+        <v>7054427</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125539227</v>
+        <v>125539222</v>
       </c>
       <c r="B25" t="n">
-        <v>80099</v>
+        <v>91220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600060</v>
+        <v>600042</v>
       </c>
       <c r="R25" t="n">
-        <v>7054552</v>
+        <v>7054425</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3110,32 +3110,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125539222</v>
+        <v>125539227</v>
       </c>
       <c r="B26" t="n">
-        <v>91220</v>
+        <v>80099</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600042</v>
+        <v>600060</v>
       </c>
       <c r="R26" t="n">
-        <v>7054425</v>
+        <v>7054552</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125539237</v>
+        <v>125546864</v>
       </c>
       <c r="B33" t="n">
-        <v>82779</v>
+        <v>78967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3808,37 +3808,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>600033</v>
+        <v>600102</v>
       </c>
       <c r="R33" t="n">
-        <v>7054517</v>
+        <v>7054399</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3876,28 +3879,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125546864</v>
+        <v>125539237</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>82779</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3905,40 +3909,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>600102</v>
+        <v>600033</v>
       </c>
       <c r="R34" t="n">
-        <v>7054399</v>
+        <v>7054517</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3976,19 +3977,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>125499358</v>
       </c>
       <c r="B7" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125539229</v>
       </c>
       <c r="B9" t="n">
-        <v>91170</v>
+        <v>91177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>125539239</v>
       </c>
       <c r="B10" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>125546798</v>
       </c>
       <c r="B12" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125539228</v>
+        <v>125539238</v>
       </c>
       <c r="B14" t="n">
-        <v>91170</v>
+        <v>82779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,21 +1939,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600053</v>
+        <v>600058</v>
       </c>
       <c r="R14" t="n">
-        <v>7054518</v>
+        <v>7054532</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2025,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125539238</v>
+        <v>125539228</v>
       </c>
       <c r="B15" t="n">
-        <v>82779</v>
+        <v>91177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,21 +2036,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600058</v>
+        <v>600053</v>
       </c>
       <c r="R15" t="n">
-        <v>7054532</v>
+        <v>7054518</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2628,7 +2628,7 @@
         <v>125539241</v>
       </c>
       <c r="B21" t="n">
-        <v>96450</v>
+        <v>96457</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>125539225</v>
       </c>
       <c r="B22" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>125539230</v>
       </c>
       <c r="B23" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>125539222</v>
       </c>
       <c r="B25" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>125539223</v>
       </c>
       <c r="B27" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>125539224</v>
       </c>
       <c r="B28" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>125539220</v>
       </c>
       <c r="B32" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125546864</v>
+        <v>125539237</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>82779</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3808,40 +3808,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>600102</v>
+        <v>600033</v>
       </c>
       <c r="R33" t="n">
-        <v>7054399</v>
+        <v>7054517</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3879,29 +3876,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125539237</v>
+        <v>125546864</v>
       </c>
       <c r="B34" t="n">
-        <v>82779</v>
+        <v>78967</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3909,37 +3905,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>600033</v>
+        <v>600102</v>
       </c>
       <c r="R34" t="n">
-        <v>7054517</v>
+        <v>7054399</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3977,18 +3976,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -3797,10 +3797,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125539237</v>
+        <v>125546864</v>
       </c>
       <c r="B33" t="n">
-        <v>82779</v>
+        <v>78967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3808,37 +3808,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>600033</v>
+        <v>600102</v>
       </c>
       <c r="R33" t="n">
-        <v>7054517</v>
+        <v>7054399</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3876,28 +3879,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125546864</v>
+        <v>125539237</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>82779</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3905,40 +3909,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>600102</v>
+        <v>600033</v>
       </c>
       <c r="R34" t="n">
-        <v>7054399</v>
+        <v>7054517</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3976,19 +3977,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,7 +790,7 @@
         <v>125500946</v>
       </c>
       <c r="B3" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125499915</v>
       </c>
       <c r="B4" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>125500716</v>
       </c>
       <c r="B5" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>125500211</v>
       </c>
       <c r="B6" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>125499358</v>
       </c>
       <c r="B7" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>125502458</v>
       </c>
       <c r="B8" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125539229</v>
       </c>
       <c r="B9" t="n">
-        <v>91177</v>
+        <v>91178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>125539239</v>
       </c>
       <c r="B10" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>125539231</v>
       </c>
       <c r="B11" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,38 +1720,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125546798</v>
+        <v>125546946</v>
       </c>
       <c r="B12" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600057</v>
+        <v>600111</v>
       </c>
       <c r="R12" t="n">
-        <v>7054319</v>
+        <v>7054404</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,13 +1797,17 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1822,38 +1826,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125546946</v>
+        <v>125546798</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>98355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1861,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600111</v>
+        <v>600057</v>
       </c>
       <c r="R13" t="n">
-        <v>7054404</v>
+        <v>7054319</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,17 +1903,13 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>125539238</v>
       </c>
       <c r="B14" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>125539228</v>
       </c>
       <c r="B15" t="n">
-        <v>91177</v>
+        <v>91178</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>125546783</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>125539232</v>
       </c>
       <c r="B18" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>125546824</v>
       </c>
       <c r="B19" t="n">
-        <v>80098</v>
+        <v>80099</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125539234</v>
       </c>
       <c r="B20" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>125539241</v>
       </c>
       <c r="B21" t="n">
-        <v>96457</v>
+        <v>96460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>125539225</v>
       </c>
       <c r="B22" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>125539230</v>
       </c>
       <c r="B23" t="n">
-        <v>91520</v>
+        <v>91524</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>125539235</v>
       </c>
       <c r="B24" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125539222</v>
+        <v>125539227</v>
       </c>
       <c r="B25" t="n">
-        <v>91227</v>
+        <v>80100</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600042</v>
+        <v>600060</v>
       </c>
       <c r="R25" t="n">
-        <v>7054425</v>
+        <v>7054552</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3110,32 +3110,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125539227</v>
+        <v>125539222</v>
       </c>
       <c r="B26" t="n">
-        <v>80099</v>
+        <v>91228</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600060</v>
+        <v>600042</v>
       </c>
       <c r="R26" t="n">
-        <v>7054552</v>
+        <v>7054425</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3210,7 +3210,7 @@
         <v>125539223</v>
       </c>
       <c r="B27" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>125539224</v>
       </c>
       <c r="B28" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>125539219</v>
       </c>
       <c r="B29" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>125539233</v>
       </c>
       <c r="B30" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>125547007</v>
       </c>
       <c r="B31" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>125539220</v>
       </c>
       <c r="B32" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>125546864</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>125539237</v>
       </c>
       <c r="B34" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3992,6 +3992,1991 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126049680</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>599885</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7054542</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall. "Skalade" grangrenar precis intill.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126051874</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91228</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>599966</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7054291</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126050156</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79586</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>599849</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7054360</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126049400</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91246</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>599855</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7054560</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126050308</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91524</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>658</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>599845</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7054328</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126051995</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91246</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>599997</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7054327</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126051788</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>599973</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7054239</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126049913</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>599817</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7054449</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126050100</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>599849</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7054361</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126048270</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>599823</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7054558</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126049595</v>
+      </c>
+      <c r="B45" t="n">
+        <v>75067</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>599888</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7054532</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126050300</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91682</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>599845</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7054329</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126050019</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>599821</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7054422</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126051739</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>599977</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7054216</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126050066</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Antemyrorna, Antemyrorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>599854</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7054375</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126049955</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91248</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>599798</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7054459</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126051627</v>
+      </c>
+      <c r="B51" t="n">
+        <v>96460</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>599926</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7054220</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126051767</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>599967</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7054228</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126051822</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91635</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>599974</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7054254</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126051924</v>
+      </c>
+      <c r="B54" t="n">
+        <v>97212</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>599973</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7054300</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -2819,10 +2819,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125539230</v>
+        <v>125539235</v>
       </c>
       <c r="B23" t="n">
-        <v>91524</v>
+        <v>80071</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600030</v>
+        <v>600048</v>
       </c>
       <c r="R23" t="n">
-        <v>7054566</v>
+        <v>7054427</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125539235</v>
+        <v>125539230</v>
       </c>
       <c r="B24" t="n">
-        <v>80071</v>
+        <v>91524</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2927,21 +2927,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600048</v>
+        <v>600030</v>
       </c>
       <c r="R24" t="n">
-        <v>7054427</v>
+        <v>7054566</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125500946</v>
       </c>
       <c r="B3" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125499915</v>
       </c>
       <c r="B4" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>125500211</v>
       </c>
       <c r="B6" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>125499358</v>
       </c>
       <c r="B7" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125539229</v>
       </c>
       <c r="B9" t="n">
-        <v>91178</v>
+        <v>91182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>125539239</v>
       </c>
       <c r="B10" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>125539231</v>
       </c>
       <c r="B11" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>125546798</v>
       </c>
       <c r="B13" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>125539238</v>
       </c>
       <c r="B14" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>125539228</v>
       </c>
       <c r="B15" t="n">
-        <v>91178</v>
+        <v>91182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125546783</v>
+        <v>125539226</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,40 +2133,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600045</v>
+        <v>600033</v>
       </c>
       <c r="R16" t="n">
-        <v>7054287</v>
+        <v>7054530</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2198,35 +2200,39 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gammalt bohål 1,5m upp i död gran. 4-4.5cm diameter</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125539226</v>
+        <v>125546783</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2234,42 +2240,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600033</v>
+        <v>600045</v>
       </c>
       <c r="R17" t="n">
-        <v>7054530</v>
+        <v>7054287</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2301,29 +2305,25 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gammalt bohål 1,5m upp i död gran. 4-4.5cm diameter</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2333,7 +2333,7 @@
         <v>125539232</v>
       </c>
       <c r="B18" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>125546824</v>
       </c>
       <c r="B19" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125539234</v>
       </c>
       <c r="B20" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>125539241</v>
       </c>
       <c r="B21" t="n">
-        <v>96460</v>
+        <v>96464</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>125539225</v>
       </c>
       <c r="B22" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>125539235</v>
       </c>
       <c r="B23" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>125539230</v>
       </c>
       <c r="B24" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>125539227</v>
       </c>
       <c r="B25" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>125539222</v>
       </c>
       <c r="B26" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125539223</v>
+        <v>125539219</v>
       </c>
       <c r="B27" t="n">
-        <v>91228</v>
+        <v>75067</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3218,21 +3218,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600053</v>
+        <v>600032</v>
       </c>
       <c r="R27" t="n">
-        <v>7054518</v>
+        <v>7054519</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3304,10 +3304,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125539224</v>
+        <v>125539223</v>
       </c>
       <c r="B28" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600042</v>
+        <v>600053</v>
       </c>
       <c r="R28" t="n">
-        <v>7054542</v>
+        <v>7054518</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125539219</v>
+        <v>125539224</v>
       </c>
       <c r="B29" t="n">
-        <v>75067</v>
+        <v>91232</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3412,21 +3412,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>600032</v>
+        <v>600042</v>
       </c>
       <c r="R29" t="n">
-        <v>7054519</v>
+        <v>7054542</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3501,7 +3501,7 @@
         <v>125539233</v>
       </c>
       <c r="B30" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>125539220</v>
       </c>
       <c r="B32" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125546864</v>
+        <v>125539237</v>
       </c>
       <c r="B33" t="n">
-        <v>78968</v>
+        <v>82784</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3808,40 +3808,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>600102</v>
+        <v>600033</v>
       </c>
       <c r="R33" t="n">
-        <v>7054399</v>
+        <v>7054517</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3879,29 +3876,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125539237</v>
+        <v>125546864</v>
       </c>
       <c r="B34" t="n">
-        <v>82780</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3909,37 +3905,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>600033</v>
+        <v>600102</v>
       </c>
       <c r="R34" t="n">
-        <v>7054517</v>
+        <v>7054399</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3977,18 +3976,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4105,7 +4105,7 @@
         <v>126051874</v>
       </c>
       <c r="B36" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>126050156</v>
       </c>
       <c r="B37" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>126049400</v>
       </c>
       <c r="B38" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>126050308</v>
       </c>
       <c r="B39" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>126051995</v>
       </c>
       <c r="B40" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>126051788</v>
       </c>
       <c r="B41" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>126049913</v>
       </c>
       <c r="B42" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>126048270</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>126050300</v>
       </c>
       <c r="B46" t="n">
-        <v>91682</v>
+        <v>91686</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>126050066</v>
       </c>
       <c r="B49" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>126049955</v>
       </c>
       <c r="B50" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>126051627</v>
       </c>
       <c r="B51" t="n">
-        <v>96460</v>
+        <v>96464</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5791,27 +5791,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126051822</v>
+        <v>126051924</v>
       </c>
       <c r="B53" t="n">
-        <v>91635</v>
+        <v>97216</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5821,10 +5826,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599974</v>
+        <v>599973</v>
       </c>
       <c r="R53" t="n">
-        <v>7054254</v>
+        <v>7054300</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5883,32 +5888,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126051924</v>
+        <v>126051822</v>
       </c>
       <c r="B54" t="n">
-        <v>97212</v>
+        <v>91639</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599973</v>
+        <v>599974</v>
       </c>
       <c r="R54" t="n">
-        <v>7054300</v>
+        <v>7054254</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -1720,38 +1720,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125546946</v>
+        <v>125546798</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600111</v>
+        <v>600057</v>
       </c>
       <c r="R12" t="n">
-        <v>7054404</v>
+        <v>7054319</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,17 +1797,13 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1826,38 +1822,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125546798</v>
+        <v>125546946</v>
       </c>
       <c r="B13" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1865,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600057</v>
+        <v>600111</v>
       </c>
       <c r="R13" t="n">
-        <v>7054319</v>
+        <v>7054404</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1903,13 +1899,17 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125539226</v>
+        <v>125546783</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,42 +2133,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600033</v>
+        <v>600045</v>
       </c>
       <c r="R16" t="n">
-        <v>7054530</v>
+        <v>7054287</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2200,39 +2198,35 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gammalt bohål 1,5m upp i död gran. 4-4.5cm diameter</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125546783</v>
+        <v>125539226</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,40 +2234,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600045</v>
+        <v>600033</v>
       </c>
       <c r="R17" t="n">
-        <v>7054287</v>
+        <v>7054530</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2305,25 +2301,29 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gammalt bohål 1,5m upp i död gran. 4-4.5cm diameter</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,7 +1218,7 @@
         <v>125499358</v>
       </c>
       <c r="B7" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1720,38 +1720,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125546798</v>
+        <v>125546946</v>
       </c>
       <c r="B12" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600057</v>
+        <v>600111</v>
       </c>
       <c r="R12" t="n">
-        <v>7054319</v>
+        <v>7054404</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,13 +1797,17 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1822,38 +1826,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125546946</v>
+        <v>125546798</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1861,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600111</v>
+        <v>600057</v>
       </c>
       <c r="R13" t="n">
-        <v>7054404</v>
+        <v>7054319</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,17 +1903,13 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>125539241</v>
       </c>
       <c r="B21" t="n">
-        <v>96464</v>
+        <v>96465</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125539235</v>
+        <v>125539230</v>
       </c>
       <c r="B23" t="n">
-        <v>80075</v>
+        <v>91528</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600048</v>
+        <v>600030</v>
       </c>
       <c r="R23" t="n">
-        <v>7054427</v>
+        <v>7054566</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125539230</v>
+        <v>125539235</v>
       </c>
       <c r="B24" t="n">
-        <v>91528</v>
+        <v>80075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2927,21 +2927,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600030</v>
+        <v>600048</v>
       </c>
       <c r="R24" t="n">
-        <v>7054566</v>
+        <v>7054427</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125539227</v>
+        <v>125539222</v>
       </c>
       <c r="B25" t="n">
-        <v>80104</v>
+        <v>91232</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600060</v>
+        <v>600042</v>
       </c>
       <c r="R25" t="n">
-        <v>7054552</v>
+        <v>7054425</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3110,32 +3110,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125539222</v>
+        <v>125539227</v>
       </c>
       <c r="B26" t="n">
-        <v>91232</v>
+        <v>80104</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600042</v>
+        <v>600060</v>
       </c>
       <c r="R26" t="n">
-        <v>7054425</v>
+        <v>7054552</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4985,45 +4985,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126049595</v>
+        <v>126050300</v>
       </c>
       <c r="B45" t="n">
-        <v>75067</v>
+        <v>91686</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599888</v>
+        <v>599845</v>
       </c>
       <c r="R45" t="n">
-        <v>7054532</v>
+        <v>7054329</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5082,45 +5082,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126050300</v>
+        <v>126049595</v>
       </c>
       <c r="B46" t="n">
-        <v>91686</v>
+        <v>75067</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599845</v>
+        <v>599888</v>
       </c>
       <c r="R46" t="n">
-        <v>7054329</v>
+        <v>7054532</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5286,10 +5286,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126051739</v>
+        <v>126050066</v>
       </c>
       <c r="B48" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5297,39 +5297,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Antemyrorna, Antemyrorna, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599977</v>
+        <v>599854</v>
       </c>
       <c r="R48" t="n">
-        <v>7054216</v>
+        <v>7054375</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5362,11 +5357,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5393,10 +5383,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126050066</v>
+        <v>126051739</v>
       </c>
       <c r="B49" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5404,34 +5394,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Antemyrorna, Antemyrorna, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599854</v>
+        <v>599977</v>
       </c>
       <c r="R49" t="n">
-        <v>7054375</v>
+        <v>7054216</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5464,6 +5459,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5490,45 +5490,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126049955</v>
+        <v>126051627</v>
       </c>
       <c r="B50" t="n">
-        <v>91252</v>
+        <v>96465</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599798</v>
+        <v>599926</v>
       </c>
       <c r="R50" t="n">
-        <v>7054459</v>
+        <v>7054220</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5587,45 +5587,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126051627</v>
+        <v>126049955</v>
       </c>
       <c r="B51" t="n">
-        <v>96464</v>
+        <v>91252</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599926</v>
+        <v>599798</v>
       </c>
       <c r="R51" t="n">
-        <v>7054220</v>
+        <v>7054459</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5794,7 +5794,7 @@
         <v>126051924</v>
       </c>
       <c r="B53" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5978,6 +5978,2957 @@
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126125252</v>
+      </c>
+      <c r="B55" t="n">
+        <v>96465</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>600020</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7054308</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126125225</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>658</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>600142</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7054429</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126125232</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91934</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>67</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>599859</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7054343</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126125220</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91250</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>600131</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7054572</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126125221</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>600131</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7054572</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126125235</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91250</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>600140</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7054408</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126125230</v>
+      </c>
+      <c r="B61" t="n">
+        <v>100494</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>600150</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7054524</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126125250</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>600123</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7054194</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126125249</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91228</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>600036</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7054276</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126125222</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>600150</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7054444</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126125223</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80104</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>600114</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7054516</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126125242</v>
+      </c>
+      <c r="B66" t="n">
+        <v>96465</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>600029</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7054403</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126125247</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>600058</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7054262</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126125227</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>600115</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7054516</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126125237</v>
+      </c>
+      <c r="B69" t="n">
+        <v>82784</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>600038</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7054626</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126125245</v>
+      </c>
+      <c r="B70" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>600027</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7054254</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126125228</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>600138</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7054474</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126125216</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91407</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>599849</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7054530</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126125231</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91934</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>67</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>599886</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7054530</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126125243</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>600068</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7054218</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>126125240</v>
+      </c>
+      <c r="B75" t="n">
+        <v>96465</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>600094</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7054569</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126125246</v>
+      </c>
+      <c r="B76" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>600024</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7054347</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>126125248</v>
+      </c>
+      <c r="B77" t="n">
+        <v>56834</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>600244</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7054641</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126125224</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79979</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>600133</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7054468</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126125229</v>
+      </c>
+      <c r="B79" t="n">
+        <v>80111</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>600133</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7054468</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126125218</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91197</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>600128</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7054464</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>126125238</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80110</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>600133</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7054468</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>126125239</v>
+      </c>
+      <c r="B82" t="n">
+        <v>96465</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>600142</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7054514</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126125244</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>600060</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7054259</v>
+      </c>
+      <c r="S83" t="n">
+        <v>15</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126125217</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91197</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>600006</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7054406</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -3207,10 +3207,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125539219</v>
+        <v>125539223</v>
       </c>
       <c r="B27" t="n">
-        <v>75067</v>
+        <v>91232</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3218,21 +3218,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600032</v>
+        <v>600053</v>
       </c>
       <c r="R27" t="n">
-        <v>7054519</v>
+        <v>7054518</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125539223</v>
+        <v>125539224</v>
       </c>
       <c r="B28" t="n">
         <v>91232</v>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600053</v>
+        <v>600042</v>
       </c>
       <c r="R28" t="n">
-        <v>7054518</v>
+        <v>7054542</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125539224</v>
+        <v>125539219</v>
       </c>
       <c r="B29" t="n">
-        <v>91232</v>
+        <v>75067</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3412,21 +3412,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>600042</v>
+        <v>600032</v>
       </c>
       <c r="R29" t="n">
-        <v>7054542</v>
+        <v>7054519</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4985,45 +4985,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126050300</v>
+        <v>126049595</v>
       </c>
       <c r="B45" t="n">
-        <v>91686</v>
+        <v>75067</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599845</v>
+        <v>599888</v>
       </c>
       <c r="R45" t="n">
-        <v>7054329</v>
+        <v>7054532</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5082,45 +5082,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126049595</v>
+        <v>126050300</v>
       </c>
       <c r="B46" t="n">
-        <v>75067</v>
+        <v>91686</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599888</v>
+        <v>599845</v>
       </c>
       <c r="R46" t="n">
-        <v>7054532</v>
+        <v>7054329</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -3207,10 +3207,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125539223</v>
+        <v>125539219</v>
       </c>
       <c r="B27" t="n">
-        <v>91232</v>
+        <v>75067</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3218,21 +3218,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600053</v>
+        <v>600032</v>
       </c>
       <c r="R27" t="n">
-        <v>7054518</v>
+        <v>7054519</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125539224</v>
+        <v>125539223</v>
       </c>
       <c r="B28" t="n">
         <v>91232</v>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600042</v>
+        <v>600053</v>
       </c>
       <c r="R28" t="n">
-        <v>7054542</v>
+        <v>7054518</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125539219</v>
+        <v>125539224</v>
       </c>
       <c r="B29" t="n">
-        <v>75067</v>
+        <v>91232</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3412,21 +3412,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>600032</v>
+        <v>600042</v>
       </c>
       <c r="R29" t="n">
-        <v>7054519</v>
+        <v>7054542</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -5286,10 +5286,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126050066</v>
+        <v>126051739</v>
       </c>
       <c r="B48" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5297,34 +5297,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Antemyrorna, Antemyrorna, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599854</v>
+        <v>599977</v>
       </c>
       <c r="R48" t="n">
-        <v>7054375</v>
+        <v>7054216</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5357,6 +5362,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5383,10 +5393,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126051739</v>
+        <v>126050066</v>
       </c>
       <c r="B49" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5394,39 +5404,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Antemyrorna, Antemyrorna, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599977</v>
+        <v>599854</v>
       </c>
       <c r="R49" t="n">
-        <v>7054216</v>
+        <v>7054375</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5459,11 +5464,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125500872</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>125500946</v>
       </c>
       <c r="B3" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125499915</v>
       </c>
       <c r="B4" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>125500716</v>
       </c>
       <c r="B5" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>125500211</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>125499358</v>
       </c>
       <c r="B7" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>125502458</v>
       </c>
       <c r="B8" t="n">
-        <v>58130</v>
+        <v>58131</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125539229</v>
       </c>
       <c r="B9" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>125539239</v>
       </c>
       <c r="B10" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>125539231</v>
       </c>
       <c r="B11" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,38 +1720,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125546946</v>
+        <v>125546798</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>98362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600111</v>
+        <v>600057</v>
       </c>
       <c r="R12" t="n">
-        <v>7054404</v>
+        <v>7054319</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,17 +1797,13 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1826,38 +1822,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125546798</v>
+        <v>125546946</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1865,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600057</v>
+        <v>600111</v>
       </c>
       <c r="R13" t="n">
-        <v>7054319</v>
+        <v>7054404</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1903,13 +1899,17 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>125539238</v>
       </c>
       <c r="B14" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>125539228</v>
       </c>
       <c r="B15" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125546783</v>
+        <v>125539226</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,40 +2133,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600045</v>
+        <v>600033</v>
       </c>
       <c r="R16" t="n">
-        <v>7054287</v>
+        <v>7054530</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2198,35 +2200,39 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gammalt bohål 1,5m upp i död gran. 4-4.5cm diameter</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125539226</v>
+        <v>125546783</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2234,42 +2240,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600033</v>
+        <v>600045</v>
       </c>
       <c r="R17" t="n">
-        <v>7054530</v>
+        <v>7054287</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2301,29 +2305,25 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gammalt bohål 1,5m upp i död gran. 4-4.5cm diameter</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2333,7 +2333,7 @@
         <v>125539232</v>
       </c>
       <c r="B18" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>125546824</v>
       </c>
       <c r="B19" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125539234</v>
       </c>
       <c r="B20" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>125539241</v>
       </c>
       <c r="B21" t="n">
-        <v>96465</v>
+        <v>96467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>125539225</v>
       </c>
       <c r="B22" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>125539230</v>
       </c>
       <c r="B23" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>125539235</v>
       </c>
       <c r="B24" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>125539222</v>
       </c>
       <c r="B25" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>125539227</v>
       </c>
       <c r="B26" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125539219</v>
+        <v>125539223</v>
       </c>
       <c r="B27" t="n">
-        <v>75067</v>
+        <v>91234</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3218,21 +3218,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600032</v>
+        <v>600053</v>
       </c>
       <c r="R27" t="n">
-        <v>7054519</v>
+        <v>7054518</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3304,10 +3304,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125539223</v>
+        <v>125539224</v>
       </c>
       <c r="B28" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600053</v>
+        <v>600042</v>
       </c>
       <c r="R28" t="n">
-        <v>7054518</v>
+        <v>7054542</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125539224</v>
+        <v>125539219</v>
       </c>
       <c r="B29" t="n">
-        <v>91232</v>
+        <v>75068</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3412,21 +3412,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>600042</v>
+        <v>600032</v>
       </c>
       <c r="R29" t="n">
-        <v>7054542</v>
+        <v>7054519</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3501,7 +3501,7 @@
         <v>125539233</v>
       </c>
       <c r="B30" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>125547007</v>
       </c>
       <c r="B31" t="n">
-        <v>58130</v>
+        <v>58131</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>125539220</v>
       </c>
       <c r="B32" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>125539237</v>
       </c>
       <c r="B33" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>125546864</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>126049680</v>
       </c>
       <c r="B35" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>126051874</v>
       </c>
       <c r="B36" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>126050156</v>
       </c>
       <c r="B37" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>126049400</v>
       </c>
       <c r="B38" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>126050308</v>
       </c>
       <c r="B39" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>126051995</v>
       </c>
       <c r="B40" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>126051788</v>
       </c>
       <c r="B41" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>126049913</v>
       </c>
       <c r="B42" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>126050100</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>126048270</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>126049595</v>
       </c>
       <c r="B45" t="n">
-        <v>75067</v>
+        <v>75068</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>126050300</v>
       </c>
       <c r="B46" t="n">
-        <v>91686</v>
+        <v>91688</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>126050019</v>
       </c>
       <c r="B47" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5286,10 +5286,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126051739</v>
+        <v>126050066</v>
       </c>
       <c r="B48" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5297,39 +5297,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Antemyrorna, Antemyrorna, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599977</v>
+        <v>599854</v>
       </c>
       <c r="R48" t="n">
-        <v>7054216</v>
+        <v>7054375</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5362,11 +5357,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5393,10 +5383,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126050066</v>
+        <v>126051739</v>
       </c>
       <c r="B49" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5404,34 +5394,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Antemyrorna, Antemyrorna, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599854</v>
+        <v>599977</v>
       </c>
       <c r="R49" t="n">
-        <v>7054375</v>
+        <v>7054216</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5464,6 +5459,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5490,45 +5490,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126051627</v>
+        <v>126049955</v>
       </c>
       <c r="B50" t="n">
-        <v>96465</v>
+        <v>91254</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599926</v>
+        <v>599798</v>
       </c>
       <c r="R50" t="n">
-        <v>7054220</v>
+        <v>7054459</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5587,45 +5587,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126049955</v>
+        <v>126051627</v>
       </c>
       <c r="B51" t="n">
-        <v>91252</v>
+        <v>96467</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599798</v>
+        <v>599926</v>
       </c>
       <c r="R51" t="n">
-        <v>7054459</v>
+        <v>7054220</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5687,7 +5687,7 @@
         <v>126051767</v>
       </c>
       <c r="B52" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5791,32 +5791,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126051924</v>
+        <v>126051822</v>
       </c>
       <c r="B53" t="n">
-        <v>97217</v>
+        <v>91641</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5826,10 +5821,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599973</v>
+        <v>599974</v>
       </c>
       <c r="R53" t="n">
-        <v>7054300</v>
+        <v>7054254</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5888,27 +5883,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126051822</v>
+        <v>126051924</v>
       </c>
       <c r="B54" t="n">
-        <v>91639</v>
+        <v>97219</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599974</v>
+        <v>599973</v>
       </c>
       <c r="R54" t="n">
-        <v>7054254</v>
+        <v>7054300</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5983,7 +5983,7 @@
         <v>126125252</v>
       </c>
       <c r="B55" t="n">
-        <v>96465</v>
+        <v>96467</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>126125225</v>
       </c>
       <c r="B56" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>126125232</v>
       </c>
       <c r="B57" t="n">
-        <v>91934</v>
+        <v>91936</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>126125220</v>
       </c>
       <c r="B58" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>126125221</v>
       </c>
       <c r="B59" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6478,32 +6478,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126125235</v>
+        <v>126125230</v>
       </c>
       <c r="B60" t="n">
-        <v>91250</v>
+        <v>100496</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600140</v>
+        <v>600150</v>
       </c>
       <c r="R60" t="n">
-        <v>7054408</v>
+        <v>7054524</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6575,32 +6575,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126125230</v>
+        <v>126125235</v>
       </c>
       <c r="B61" t="n">
-        <v>100494</v>
+        <v>91252</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1365</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>600150</v>
+        <v>600140</v>
       </c>
       <c r="R61" t="n">
-        <v>7054524</v>
+        <v>7054408</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6675,7 +6675,7 @@
         <v>126125250</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>126125249</v>
       </c>
       <c r="B63" t="n">
-        <v>91228</v>
+        <v>91230</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>126125222</v>
       </c>
       <c r="B64" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>126125223</v>
       </c>
       <c r="B65" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7070,32 +7070,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126125242</v>
+        <v>126125247</v>
       </c>
       <c r="B66" t="n">
-        <v>96465</v>
+        <v>80076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>600029</v>
+        <v>600058</v>
       </c>
       <c r="R66" t="n">
-        <v>7054403</v>
+        <v>7054262</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7135,12 +7135,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7167,32 +7167,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126125247</v>
+        <v>126125242</v>
       </c>
       <c r="B67" t="n">
-        <v>80075</v>
+        <v>96467</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7202,10 +7202,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>600058</v>
+        <v>600029</v>
       </c>
       <c r="R67" t="n">
-        <v>7054262</v>
+        <v>7054403</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7232,12 +7232,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7267,7 +7267,7 @@
         <v>126125227</v>
       </c>
       <c r="B68" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7361,10 +7361,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126125237</v>
+        <v>126125245</v>
       </c>
       <c r="B69" t="n">
-        <v>82784</v>
+        <v>80076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7372,21 +7372,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>600038</v>
+        <v>600027</v>
       </c>
       <c r="R69" t="n">
-        <v>7054626</v>
+        <v>7054254</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7426,12 +7426,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7458,10 +7458,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126125245</v>
+        <v>126125237</v>
       </c>
       <c r="B70" t="n">
-        <v>80075</v>
+        <v>82785</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7469,21 +7469,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>600027</v>
+        <v>600038</v>
       </c>
       <c r="R70" t="n">
-        <v>7054254</v>
+        <v>7054626</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7523,12 +7523,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7558,7 +7558,7 @@
         <v>126125228</v>
       </c>
       <c r="B71" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>126125216</v>
       </c>
       <c r="B72" t="n">
-        <v>91407</v>
+        <v>91409</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>126125231</v>
       </c>
       <c r="B73" t="n">
-        <v>91934</v>
+        <v>91936</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>126125243</v>
       </c>
       <c r="B74" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>126125240</v>
       </c>
       <c r="B75" t="n">
-        <v>96465</v>
+        <v>96467</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>126125246</v>
       </c>
       <c r="B76" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>126125248</v>
       </c>
       <c r="B77" t="n">
-        <v>56834</v>
+        <v>56835</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         <v>126125224</v>
       </c>
       <c r="B78" t="n">
-        <v>79979</v>
+        <v>79980</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>126125229</v>
       </c>
       <c r="B79" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>126125218</v>
       </c>
       <c r="B80" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>126125238</v>
       </c>
       <c r="B81" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8630,45 +8630,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126125239</v>
+        <v>126125244</v>
       </c>
       <c r="B82" t="n">
-        <v>96465</v>
+        <v>57652</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>600142</v>
+        <v>600060</v>
       </c>
       <c r="R82" t="n">
-        <v>7054514</v>
+        <v>7054259</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8695,12 +8700,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8727,50 +8737,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126125244</v>
+        <v>126125239</v>
       </c>
       <c r="B83" t="n">
-        <v>57651</v>
+        <v>96467</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>600060</v>
+        <v>600142</v>
       </c>
       <c r="R83" t="n">
-        <v>7054259</v>
+        <v>7054514</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8797,17 +8802,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8837,7 +8837,7 @@
         <v>126125217</v>
       </c>
       <c r="B84" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -2122,10 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125539226</v>
+        <v>125546783</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,42 +2133,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600033</v>
+        <v>600045</v>
       </c>
       <c r="R16" t="n">
-        <v>7054530</v>
+        <v>7054287</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2200,39 +2198,35 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gammalt bohål 1,5m upp i död gran. 4-4.5cm diameter</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125546783</v>
+        <v>125539226</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,40 +2234,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lövsjön, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600045</v>
+        <v>600033</v>
       </c>
       <c r="R17" t="n">
-        <v>7054287</v>
+        <v>7054530</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2305,25 +2301,29 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gammalt bohål 1,5m upp i död gran. 4-4.5cm diameter</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -4985,45 +4985,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126049595</v>
+        <v>126050300</v>
       </c>
       <c r="B45" t="n">
-        <v>75068</v>
+        <v>91688</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599888</v>
+        <v>599845</v>
       </c>
       <c r="R45" t="n">
-        <v>7054532</v>
+        <v>7054329</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5082,45 +5082,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126050300</v>
+        <v>126049595</v>
       </c>
       <c r="B46" t="n">
-        <v>91688</v>
+        <v>75068</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599845</v>
+        <v>599888</v>
       </c>
       <c r="R46" t="n">
-        <v>7054329</v>
+        <v>7054532</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -8137,53 +8137,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126125248</v>
+        <v>126125224</v>
       </c>
       <c r="B77" t="n">
-        <v>56835</v>
+        <v>79980</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>600244</v>
+        <v>600133</v>
       </c>
       <c r="R77" t="n">
-        <v>7054641</v>
+        <v>7054468</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8210,12 +8202,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8242,45 +8234,53 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126125224</v>
+        <v>126125248</v>
       </c>
       <c r="B78" t="n">
-        <v>79980</v>
+        <v>56835</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6456</v>
+        <v>102612</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>600133</v>
+        <v>600244</v>
       </c>
       <c r="R78" t="n">
-        <v>7054468</v>
+        <v>7054641</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8307,12 +8307,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>125499358</v>
       </c>
       <c r="B7" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125539229</v>
       </c>
       <c r="B9" t="n">
-        <v>91184</v>
+        <v>91186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>125539239</v>
       </c>
       <c r="B10" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>125546798</v>
       </c>
       <c r="B12" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>125539228</v>
       </c>
       <c r="B15" t="n">
-        <v>91184</v>
+        <v>91186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>125539241</v>
       </c>
       <c r="B21" t="n">
-        <v>96467</v>
+        <v>96469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>125539225</v>
       </c>
       <c r="B22" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>125539230</v>
       </c>
       <c r="B23" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>125539222</v>
       </c>
       <c r="B25" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125539223</v>
+        <v>125539224</v>
       </c>
       <c r="B27" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600053</v>
+        <v>600042</v>
       </c>
       <c r="R27" t="n">
-        <v>7054518</v>
+        <v>7054542</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3304,10 +3304,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125539224</v>
+        <v>125539223</v>
       </c>
       <c r="B28" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600042</v>
+        <v>600053</v>
       </c>
       <c r="R28" t="n">
-        <v>7054542</v>
+        <v>7054518</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>125539220</v>
       </c>
       <c r="B32" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>126051874</v>
       </c>
       <c r="B36" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>126049400</v>
       </c>
       <c r="B38" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>126050308</v>
       </c>
       <c r="B39" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>126051995</v>
       </c>
       <c r="B40" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>126050300</v>
       </c>
       <c r="B45" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>126049955</v>
       </c>
       <c r="B50" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>126051627</v>
       </c>
       <c r="B51" t="n">
-        <v>96467</v>
+        <v>96469</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>126051822</v>
       </c>
       <c r="B53" t="n">
-        <v>91641</v>
+        <v>91643</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>126051924</v>
       </c>
       <c r="B54" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5980,32 +5980,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126125252</v>
+        <v>126125225</v>
       </c>
       <c r="B55" t="n">
-        <v>96467</v>
+        <v>91532</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>600020</v>
+        <v>600142</v>
       </c>
       <c r="R55" t="n">
-        <v>7054308</v>
+        <v>7054429</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6045,12 +6045,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6077,32 +6077,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126125225</v>
+        <v>126125252</v>
       </c>
       <c r="B56" t="n">
-        <v>91530</v>
+        <v>96469</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>600142</v>
+        <v>600020</v>
       </c>
       <c r="R56" t="n">
-        <v>7054429</v>
+        <v>7054308</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6142,12 +6142,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6177,7 +6177,7 @@
         <v>126125232</v>
       </c>
       <c r="B57" t="n">
-        <v>91936</v>
+        <v>91938</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>126125220</v>
       </c>
       <c r="B58" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6368,53 +6368,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126125221</v>
+        <v>126125230</v>
       </c>
       <c r="B59" t="n">
-        <v>57652</v>
+        <v>100498</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>600131</v>
+        <v>600150</v>
       </c>
       <c r="R59" t="n">
-        <v>7054572</v>
+        <v>7054524</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6447,11 +6439,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6478,32 +6465,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126125230</v>
+        <v>126125235</v>
       </c>
       <c r="B60" t="n">
-        <v>100496</v>
+        <v>91254</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1365</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6513,10 +6500,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600150</v>
+        <v>600140</v>
       </c>
       <c r="R60" t="n">
-        <v>7054524</v>
+        <v>7054408</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6575,10 +6562,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126125235</v>
+        <v>126125250</v>
       </c>
       <c r="B61" t="n">
-        <v>91252</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6586,21 +6573,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6610,10 +6597,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>600140</v>
+        <v>600123</v>
       </c>
       <c r="R61" t="n">
-        <v>7054408</v>
+        <v>7054194</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6640,12 +6627,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6672,10 +6659,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126125250</v>
+        <v>126125221</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6683,34 +6670,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>600123</v>
+        <v>600131</v>
       </c>
       <c r="R62" t="n">
-        <v>7054194</v>
+        <v>7054572</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6737,12 +6732,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6772,7 +6772,7 @@
         <v>126125249</v>
       </c>
       <c r="B63" t="n">
-        <v>91230</v>
+        <v>91232</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7070,32 +7070,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126125247</v>
+        <v>126125242</v>
       </c>
       <c r="B66" t="n">
-        <v>80076</v>
+        <v>96469</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>600058</v>
+        <v>600029</v>
       </c>
       <c r="R66" t="n">
-        <v>7054262</v>
+        <v>7054403</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7135,12 +7135,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7167,32 +7167,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126125242</v>
+        <v>126125247</v>
       </c>
       <c r="B67" t="n">
-        <v>96467</v>
+        <v>80076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7202,10 +7202,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>600029</v>
+        <v>600058</v>
       </c>
       <c r="R67" t="n">
-        <v>7054403</v>
+        <v>7054262</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7232,12 +7232,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7655,7 +7655,7 @@
         <v>126125216</v>
       </c>
       <c r="B72" t="n">
-        <v>91409</v>
+        <v>91411</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>126125231</v>
       </c>
       <c r="B73" t="n">
-        <v>91936</v>
+        <v>91938</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>126125243</v>
       </c>
       <c r="B74" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>126125240</v>
       </c>
       <c r="B75" t="n">
-        <v>96467</v>
+        <v>96469</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>126125218</v>
       </c>
       <c r="B80" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8630,50 +8630,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126125244</v>
+        <v>126125239</v>
       </c>
       <c r="B82" t="n">
-        <v>57652</v>
+        <v>96469</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>600060</v>
+        <v>600142</v>
       </c>
       <c r="R82" t="n">
-        <v>7054259</v>
+        <v>7054514</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8700,17 +8695,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8737,45 +8727,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126125239</v>
+        <v>126125244</v>
       </c>
       <c r="B83" t="n">
-        <v>96467</v>
+        <v>57652</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>600142</v>
+        <v>600060</v>
       </c>
       <c r="R83" t="n">
-        <v>7054514</v>
+        <v>7054259</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8802,12 +8797,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8837,7 +8837,7 @@
         <v>126125217</v>
       </c>
       <c r="B84" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -5490,45 +5490,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126049955</v>
+        <v>126051627</v>
       </c>
       <c r="B50" t="n">
-        <v>91256</v>
+        <v>96469</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599798</v>
+        <v>599926</v>
       </c>
       <c r="R50" t="n">
-        <v>7054459</v>
+        <v>7054220</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5587,45 +5587,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126051627</v>
+        <v>126049955</v>
       </c>
       <c r="B51" t="n">
-        <v>96469</v>
+        <v>91256</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599926</v>
+        <v>599798</v>
       </c>
       <c r="R51" t="n">
-        <v>7054220</v>
+        <v>7054459</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5791,27 +5791,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126051822</v>
+        <v>126051924</v>
       </c>
       <c r="B53" t="n">
-        <v>91643</v>
+        <v>97221</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5821,10 +5826,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599974</v>
+        <v>599973</v>
       </c>
       <c r="R53" t="n">
-        <v>7054254</v>
+        <v>7054300</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5883,32 +5888,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126051924</v>
+        <v>126051822</v>
       </c>
       <c r="B54" t="n">
-        <v>97221</v>
+        <v>91643</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599973</v>
+        <v>599974</v>
       </c>
       <c r="R54" t="n">
-        <v>7054300</v>
+        <v>7054254</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6465,10 +6465,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126125235</v>
+        <v>126125221</v>
       </c>
       <c r="B60" t="n">
-        <v>91254</v>
+        <v>57652</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6476,34 +6476,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600140</v>
+        <v>600131</v>
       </c>
       <c r="R60" t="n">
-        <v>7054408</v>
+        <v>7054572</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6536,6 +6544,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6562,10 +6575,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126125250</v>
+        <v>126125235</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>91254</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6573,21 +6586,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6597,10 +6610,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>600123</v>
+        <v>600140</v>
       </c>
       <c r="R61" t="n">
-        <v>7054194</v>
+        <v>7054408</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6627,12 +6640,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6659,10 +6672,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126125221</v>
+        <v>126125250</v>
       </c>
       <c r="B62" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6670,42 +6683,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>600131</v>
+        <v>600123</v>
       </c>
       <c r="R62" t="n">
-        <v>7054572</v>
+        <v>7054194</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6732,17 +6737,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8630,45 +8630,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126125239</v>
+        <v>126125244</v>
       </c>
       <c r="B82" t="n">
-        <v>96469</v>
+        <v>57652</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>600142</v>
+        <v>600060</v>
       </c>
       <c r="R82" t="n">
-        <v>7054514</v>
+        <v>7054259</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8695,12 +8700,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8727,50 +8737,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126125244</v>
+        <v>126125239</v>
       </c>
       <c r="B83" t="n">
-        <v>57652</v>
+        <v>96469</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>600060</v>
+        <v>600142</v>
       </c>
       <c r="R83" t="n">
-        <v>7054259</v>
+        <v>7054514</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8797,17 +8802,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -4105,7 +4105,7 @@
         <v>126051874</v>
       </c>
       <c r="B36" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>126049400</v>
       </c>
       <c r="B38" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>126050308</v>
       </c>
       <c r="B39" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>126051995</v>
       </c>
       <c r="B40" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4985,45 +4985,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126050300</v>
+        <v>126049595</v>
       </c>
       <c r="B45" t="n">
-        <v>91690</v>
+        <v>75068</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599845</v>
+        <v>599888</v>
       </c>
       <c r="R45" t="n">
-        <v>7054329</v>
+        <v>7054532</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5082,45 +5082,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126049595</v>
+        <v>126050300</v>
       </c>
       <c r="B46" t="n">
-        <v>75068</v>
+        <v>91692</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599888</v>
+        <v>599845</v>
       </c>
       <c r="R46" t="n">
-        <v>7054532</v>
+        <v>7054329</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5490,45 +5490,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126051627</v>
+        <v>126049955</v>
       </c>
       <c r="B50" t="n">
-        <v>96469</v>
+        <v>91258</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599926</v>
+        <v>599798</v>
       </c>
       <c r="R50" t="n">
-        <v>7054220</v>
+        <v>7054459</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5587,45 +5587,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126049955</v>
+        <v>126051627</v>
       </c>
       <c r="B51" t="n">
-        <v>91256</v>
+        <v>96471</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599798</v>
+        <v>599926</v>
       </c>
       <c r="R51" t="n">
-        <v>7054459</v>
+        <v>7054220</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5794,7 +5794,7 @@
         <v>126051924</v>
       </c>
       <c r="B53" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>126051822</v>
       </c>
       <c r="B54" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5980,32 +5980,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126125225</v>
+        <v>126125252</v>
       </c>
       <c r="B55" t="n">
-        <v>91532</v>
+        <v>96471</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>600142</v>
+        <v>600020</v>
       </c>
       <c r="R55" t="n">
-        <v>7054429</v>
+        <v>7054308</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6045,12 +6045,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6077,32 +6077,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126125252</v>
+        <v>126125225</v>
       </c>
       <c r="B56" t="n">
-        <v>96469</v>
+        <v>91534</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>600020</v>
+        <v>600142</v>
       </c>
       <c r="R56" t="n">
-        <v>7054308</v>
+        <v>7054429</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6142,12 +6142,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6177,7 +6177,7 @@
         <v>126125232</v>
       </c>
       <c r="B57" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>126125220</v>
       </c>
       <c r="B58" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6368,32 +6368,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126125230</v>
+        <v>126125235</v>
       </c>
       <c r="B59" t="n">
-        <v>100498</v>
+        <v>91256</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1365</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6403,10 +6403,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>600150</v>
+        <v>600140</v>
       </c>
       <c r="R59" t="n">
-        <v>7054524</v>
+        <v>7054408</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6465,10 +6465,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126125221</v>
+        <v>126125250</v>
       </c>
       <c r="B60" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6476,42 +6476,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600131</v>
+        <v>600123</v>
       </c>
       <c r="R60" t="n">
-        <v>7054572</v>
+        <v>7054194</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6538,17 +6530,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6575,10 +6562,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126125235</v>
+        <v>126125221</v>
       </c>
       <c r="B61" t="n">
-        <v>91254</v>
+        <v>57652</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6586,34 +6573,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>600140</v>
+        <v>600131</v>
       </c>
       <c r="R61" t="n">
-        <v>7054408</v>
+        <v>7054572</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6646,6 +6641,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6672,32 +6672,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126125250</v>
+        <v>126125230</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>100500</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>600123</v>
+        <v>600150</v>
       </c>
       <c r="R62" t="n">
-        <v>7054194</v>
+        <v>7054524</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6737,12 +6737,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6772,7 +6772,7 @@
         <v>126125249</v>
       </c>
       <c r="B63" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>126125242</v>
       </c>
       <c r="B66" t="n">
-        <v>96469</v>
+        <v>96471</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7361,10 +7361,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126125245</v>
+        <v>126125237</v>
       </c>
       <c r="B69" t="n">
-        <v>80076</v>
+        <v>82785</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7372,21 +7372,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>600027</v>
+        <v>600038</v>
       </c>
       <c r="R69" t="n">
-        <v>7054254</v>
+        <v>7054626</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7426,12 +7426,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7458,10 +7458,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126125237</v>
+        <v>126125245</v>
       </c>
       <c r="B70" t="n">
-        <v>82785</v>
+        <v>80076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7469,21 +7469,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>600038</v>
+        <v>600027</v>
       </c>
       <c r="R70" t="n">
-        <v>7054626</v>
+        <v>7054254</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7523,12 +7523,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7655,7 +7655,7 @@
         <v>126125216</v>
       </c>
       <c r="B72" t="n">
-        <v>91411</v>
+        <v>91413</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>126125231</v>
       </c>
       <c r="B73" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>126125243</v>
       </c>
       <c r="B74" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>126125240</v>
       </c>
       <c r="B75" t="n">
-        <v>96469</v>
+        <v>96471</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>126125218</v>
       </c>
       <c r="B80" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8630,50 +8630,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126125244</v>
+        <v>126125239</v>
       </c>
       <c r="B82" t="n">
-        <v>57652</v>
+        <v>96471</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>600060</v>
+        <v>600142</v>
       </c>
       <c r="R82" t="n">
-        <v>7054259</v>
+        <v>7054514</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8700,17 +8695,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8737,45 +8727,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126125239</v>
+        <v>126125244</v>
       </c>
       <c r="B83" t="n">
-        <v>96469</v>
+        <v>57652</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>600142</v>
+        <v>600060</v>
       </c>
       <c r="R83" t="n">
-        <v>7054514</v>
+        <v>7054259</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8802,12 +8797,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8837,7 +8837,7 @@
         <v>126125217</v>
       </c>
       <c r="B84" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -4985,45 +4985,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126049595</v>
+        <v>126050300</v>
       </c>
       <c r="B45" t="n">
-        <v>75068</v>
+        <v>91692</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599888</v>
+        <v>599845</v>
       </c>
       <c r="R45" t="n">
-        <v>7054532</v>
+        <v>7054329</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5082,45 +5082,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126050300</v>
+        <v>126049595</v>
       </c>
       <c r="B46" t="n">
-        <v>91692</v>
+        <v>75068</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599845</v>
+        <v>599888</v>
       </c>
       <c r="R46" t="n">
-        <v>7054329</v>
+        <v>7054532</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -3998,7 +3998,7 @@
         <v>126049680</v>
       </c>
       <c r="B35" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>126051874</v>
       </c>
       <c r="B36" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>126050156</v>
       </c>
       <c r="B37" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>126049400</v>
       </c>
       <c r="B38" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>126050308</v>
       </c>
       <c r="B39" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>126051995</v>
       </c>
       <c r="B40" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>126051788</v>
       </c>
       <c r="B41" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>126049913</v>
       </c>
       <c r="B42" t="n">
-        <v>80104</v>
+        <v>80108</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>126050100</v>
       </c>
       <c r="B43" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>126048270</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4985,45 +4985,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126050300</v>
+        <v>126049595</v>
       </c>
       <c r="B45" t="n">
-        <v>91692</v>
+        <v>75072</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599845</v>
+        <v>599888</v>
       </c>
       <c r="R45" t="n">
-        <v>7054329</v>
+        <v>7054532</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5082,45 +5082,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126049595</v>
+        <v>126050300</v>
       </c>
       <c r="B46" t="n">
-        <v>75068</v>
+        <v>91696</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599888</v>
+        <v>599845</v>
       </c>
       <c r="R46" t="n">
-        <v>7054532</v>
+        <v>7054329</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5182,7 +5182,7 @@
         <v>126050019</v>
       </c>
       <c r="B47" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>126050066</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>126051739</v>
       </c>
       <c r="B49" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>126049955</v>
       </c>
       <c r="B50" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>126051627</v>
       </c>
       <c r="B51" t="n">
-        <v>96471</v>
+        <v>96475</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>126051767</v>
       </c>
       <c r="B52" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5791,32 +5791,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126051924</v>
+        <v>126051822</v>
       </c>
       <c r="B53" t="n">
-        <v>97223</v>
+        <v>91649</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5826,10 +5821,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599973</v>
+        <v>599974</v>
       </c>
       <c r="R53" t="n">
-        <v>7054300</v>
+        <v>7054254</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5888,27 +5883,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126051822</v>
+        <v>126051924</v>
       </c>
       <c r="B54" t="n">
-        <v>91645</v>
+        <v>97227</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599974</v>
+        <v>599973</v>
       </c>
       <c r="R54" t="n">
-        <v>7054254</v>
+        <v>7054300</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5980,32 +5980,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126125252</v>
+        <v>126125225</v>
       </c>
       <c r="B55" t="n">
-        <v>96471</v>
+        <v>91538</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>600020</v>
+        <v>600142</v>
       </c>
       <c r="R55" t="n">
-        <v>7054308</v>
+        <v>7054429</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6045,12 +6045,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6077,32 +6077,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126125225</v>
+        <v>126125252</v>
       </c>
       <c r="B56" t="n">
-        <v>91534</v>
+        <v>96475</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>600142</v>
+        <v>600020</v>
       </c>
       <c r="R56" t="n">
-        <v>7054429</v>
+        <v>7054308</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6142,12 +6142,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6177,7 +6177,7 @@
         <v>126125232</v>
       </c>
       <c r="B57" t="n">
-        <v>91940</v>
+        <v>91944</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>126125220</v>
       </c>
       <c r="B58" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126125235</v>
+        <v>126125250</v>
       </c>
       <c r="B59" t="n">
-        <v>91256</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6379,21 +6379,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6403,10 +6403,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>600140</v>
+        <v>600123</v>
       </c>
       <c r="R59" t="n">
-        <v>7054408</v>
+        <v>7054194</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6433,12 +6433,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6465,10 +6465,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126125250</v>
+        <v>126125221</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6476,34 +6476,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600123</v>
+        <v>600131</v>
       </c>
       <c r="R60" t="n">
-        <v>7054194</v>
+        <v>7054572</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6530,12 +6538,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6562,10 +6575,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126125221</v>
+        <v>126125235</v>
       </c>
       <c r="B61" t="n">
-        <v>57652</v>
+        <v>91260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6573,42 +6586,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>600131</v>
+        <v>600140</v>
       </c>
       <c r="R61" t="n">
-        <v>7054572</v>
+        <v>7054408</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6641,11 +6646,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6675,7 +6675,7 @@
         <v>126125230</v>
       </c>
       <c r="B62" t="n">
-        <v>100500</v>
+        <v>100504</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>126125249</v>
       </c>
       <c r="B63" t="n">
-        <v>91234</v>
+        <v>91238</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>126125222</v>
       </c>
       <c r="B64" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>126125223</v>
       </c>
       <c r="B65" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7070,32 +7070,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126125242</v>
+        <v>126125247</v>
       </c>
       <c r="B66" t="n">
-        <v>96471</v>
+        <v>80080</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>600029</v>
+        <v>600058</v>
       </c>
       <c r="R66" t="n">
-        <v>7054403</v>
+        <v>7054262</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7135,12 +7135,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7167,32 +7167,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126125247</v>
+        <v>126125242</v>
       </c>
       <c r="B67" t="n">
-        <v>80076</v>
+        <v>96475</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7202,10 +7202,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>600058</v>
+        <v>600029</v>
       </c>
       <c r="R67" t="n">
-        <v>7054262</v>
+        <v>7054403</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7232,12 +7232,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7267,7 +7267,7 @@
         <v>126125227</v>
       </c>
       <c r="B68" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7361,10 +7361,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126125237</v>
+        <v>126125245</v>
       </c>
       <c r="B69" t="n">
-        <v>82785</v>
+        <v>80080</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7372,21 +7372,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>600038</v>
+        <v>600027</v>
       </c>
       <c r="R69" t="n">
-        <v>7054626</v>
+        <v>7054254</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7426,12 +7426,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7458,10 +7458,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126125245</v>
+        <v>126125237</v>
       </c>
       <c r="B70" t="n">
-        <v>80076</v>
+        <v>82789</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7469,21 +7469,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>600027</v>
+        <v>600038</v>
       </c>
       <c r="R70" t="n">
-        <v>7054254</v>
+        <v>7054626</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7523,12 +7523,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7558,7 +7558,7 @@
         <v>126125228</v>
       </c>
       <c r="B71" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>126125216</v>
       </c>
       <c r="B72" t="n">
-        <v>91413</v>
+        <v>91417</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>126125231</v>
       </c>
       <c r="B73" t="n">
-        <v>91940</v>
+        <v>91944</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>126125243</v>
       </c>
       <c r="B74" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>126125240</v>
       </c>
       <c r="B75" t="n">
-        <v>96471</v>
+        <v>96475</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>126125246</v>
       </c>
       <c r="B76" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>126125224</v>
       </c>
       <c r="B77" t="n">
-        <v>79980</v>
+        <v>79984</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>126125248</v>
       </c>
       <c r="B78" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>126125229</v>
       </c>
       <c r="B79" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8436,10 +8436,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126125218</v>
+        <v>126125238</v>
       </c>
       <c r="B80" t="n">
-        <v>91203</v>
+        <v>80115</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8447,21 +8447,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8471,10 +8471,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>600128</v>
+        <v>600133</v>
       </c>
       <c r="R80" t="n">
-        <v>7054464</v>
+        <v>7054468</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8533,10 +8533,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126125238</v>
+        <v>126125218</v>
       </c>
       <c r="B81" t="n">
-        <v>80111</v>
+        <v>91207</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8544,21 +8544,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8568,10 +8568,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>600133</v>
+        <v>600128</v>
       </c>
       <c r="R81" t="n">
-        <v>7054468</v>
+        <v>7054464</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8633,7 +8633,7 @@
         <v>126125239</v>
       </c>
       <c r="B82" t="n">
-        <v>96471</v>
+        <v>96475</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>126125244</v>
       </c>
       <c r="B83" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>126125217</v>
       </c>
       <c r="B84" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -4490,10 +4490,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126051995</v>
+        <v>126051788</v>
       </c>
       <c r="B40" t="n">
-        <v>91260</v>
+        <v>80080</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4501,21 +4501,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599997</v>
+        <v>599973</v>
       </c>
       <c r="R40" t="n">
-        <v>7054327</v>
+        <v>7054239</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126051788</v>
+        <v>126051995</v>
       </c>
       <c r="B41" t="n">
-        <v>80080</v>
+        <v>91260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599973</v>
+        <v>599997</v>
       </c>
       <c r="R41" t="n">
-        <v>7054239</v>
+        <v>7054327</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5791,27 +5791,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126051822</v>
+        <v>126051924</v>
       </c>
       <c r="B53" t="n">
-        <v>91649</v>
+        <v>97227</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5821,10 +5826,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599974</v>
+        <v>599973</v>
       </c>
       <c r="R53" t="n">
-        <v>7054254</v>
+        <v>7054300</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5883,32 +5888,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126051924</v>
+        <v>126051822</v>
       </c>
       <c r="B54" t="n">
-        <v>97227</v>
+        <v>91649</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599973</v>
+        <v>599974</v>
       </c>
       <c r="R54" t="n">
-        <v>7054300</v>
+        <v>7054254</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6368,32 +6368,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126125250</v>
+        <v>126125230</v>
       </c>
       <c r="B59" t="n">
-        <v>78977</v>
+        <v>100504</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6403,10 +6403,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>600123</v>
+        <v>600150</v>
       </c>
       <c r="R59" t="n">
-        <v>7054194</v>
+        <v>7054524</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6433,12 +6433,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6575,10 +6575,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126125235</v>
+        <v>126125250</v>
       </c>
       <c r="B61" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6586,21 +6586,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>600140</v>
+        <v>600123</v>
       </c>
       <c r="R61" t="n">
-        <v>7054408</v>
+        <v>7054194</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6672,32 +6672,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126125230</v>
+        <v>126125235</v>
       </c>
       <c r="B62" t="n">
-        <v>100504</v>
+        <v>91260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1365</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>600150</v>
+        <v>600140</v>
       </c>
       <c r="R62" t="n">
-        <v>7054524</v>
+        <v>7054408</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7070,32 +7070,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126125247</v>
+        <v>126125242</v>
       </c>
       <c r="B66" t="n">
-        <v>80080</v>
+        <v>96475</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>600058</v>
+        <v>600029</v>
       </c>
       <c r="R66" t="n">
-        <v>7054262</v>
+        <v>7054403</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7135,12 +7135,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7167,32 +7167,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126125242</v>
+        <v>126125247</v>
       </c>
       <c r="B67" t="n">
-        <v>96475</v>
+        <v>80080</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7202,10 +7202,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>600029</v>
+        <v>600058</v>
       </c>
       <c r="R67" t="n">
-        <v>7054403</v>
+        <v>7054262</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7232,12 +7232,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8630,45 +8630,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126125239</v>
+        <v>126125244</v>
       </c>
       <c r="B82" t="n">
-        <v>96475</v>
+        <v>57656</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>600142</v>
+        <v>600060</v>
       </c>
       <c r="R82" t="n">
-        <v>7054514</v>
+        <v>7054259</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8695,12 +8700,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8727,50 +8737,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126125244</v>
+        <v>126125239</v>
       </c>
       <c r="B83" t="n">
-        <v>57656</v>
+        <v>96475</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>600060</v>
+        <v>600142</v>
       </c>
       <c r="R83" t="n">
-        <v>7054259</v>
+        <v>7054514</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8797,17 +8802,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -4490,10 +4490,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126051788</v>
+        <v>126051995</v>
       </c>
       <c r="B40" t="n">
-        <v>80080</v>
+        <v>91260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4501,21 +4501,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599973</v>
+        <v>599997</v>
       </c>
       <c r="R40" t="n">
-        <v>7054239</v>
+        <v>7054327</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126051995</v>
+        <v>126051788</v>
       </c>
       <c r="B41" t="n">
-        <v>91260</v>
+        <v>80080</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599997</v>
+        <v>599973</v>
       </c>
       <c r="R41" t="n">
-        <v>7054327</v>
+        <v>7054239</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5590,7 +5590,7 @@
         <v>126051627</v>
       </c>
       <c r="B51" t="n">
-        <v>96475</v>
+        <v>96478</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5684,50 +5684,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126051767</v>
+        <v>126051924</v>
       </c>
       <c r="B52" t="n">
-        <v>57656</v>
+        <v>97230</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>599967</v>
+        <v>599973</v>
       </c>
       <c r="R52" t="n">
-        <v>7054228</v>
+        <v>7054300</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5760,11 +5755,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5791,32 +5781,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126051924</v>
+        <v>126051822</v>
       </c>
       <c r="B53" t="n">
-        <v>97227</v>
+        <v>91649</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5826,10 +5811,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599973</v>
+        <v>599974</v>
       </c>
       <c r="R53" t="n">
-        <v>7054300</v>
+        <v>7054254</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5888,10 +5873,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126051822</v>
+        <v>126051767</v>
       </c>
       <c r="B54" t="n">
-        <v>91649</v>
+        <v>57656</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5899,29 +5884,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599974</v>
+        <v>599967</v>
       </c>
       <c r="R54" t="n">
-        <v>7054254</v>
+        <v>7054228</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5954,6 +5949,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5980,32 +5980,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126125225</v>
+        <v>126125252</v>
       </c>
       <c r="B55" t="n">
-        <v>91538</v>
+        <v>96478</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>600142</v>
+        <v>600020</v>
       </c>
       <c r="R55" t="n">
-        <v>7054429</v>
+        <v>7054308</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6045,12 +6045,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6077,32 +6077,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126125252</v>
+        <v>126125225</v>
       </c>
       <c r="B56" t="n">
-        <v>96475</v>
+        <v>91538</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>600020</v>
+        <v>600142</v>
       </c>
       <c r="R56" t="n">
-        <v>7054308</v>
+        <v>7054429</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6142,12 +6142,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6368,45 +6368,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126125230</v>
+        <v>126125221</v>
       </c>
       <c r="B59" t="n">
-        <v>100504</v>
+        <v>57656</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>600150</v>
+        <v>600131</v>
       </c>
       <c r="R59" t="n">
-        <v>7054524</v>
+        <v>7054572</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6439,6 +6447,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6465,10 +6478,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126125221</v>
+        <v>126125235</v>
       </c>
       <c r="B60" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6476,42 +6489,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600131</v>
+        <v>600140</v>
       </c>
       <c r="R60" t="n">
-        <v>7054572</v>
+        <v>7054408</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6544,11 +6549,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6575,32 +6575,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126125250</v>
+        <v>126125230</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>100507</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>600123</v>
+        <v>600150</v>
       </c>
       <c r="R61" t="n">
-        <v>7054194</v>
+        <v>7054524</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6672,10 +6672,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126125235</v>
+        <v>126125250</v>
       </c>
       <c r="B62" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6683,21 +6683,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>600140</v>
+        <v>600123</v>
       </c>
       <c r="R62" t="n">
-        <v>7054408</v>
+        <v>7054194</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6737,12 +6737,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7070,32 +7070,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126125242</v>
+        <v>126125247</v>
       </c>
       <c r="B66" t="n">
-        <v>96475</v>
+        <v>80080</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>600029</v>
+        <v>600058</v>
       </c>
       <c r="R66" t="n">
-        <v>7054403</v>
+        <v>7054262</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7135,12 +7135,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7167,32 +7167,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126125247</v>
+        <v>126125242</v>
       </c>
       <c r="B67" t="n">
-        <v>80080</v>
+        <v>96478</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7202,10 +7202,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>600058</v>
+        <v>600029</v>
       </c>
       <c r="R67" t="n">
-        <v>7054262</v>
+        <v>7054403</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7232,12 +7232,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7361,10 +7361,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126125245</v>
+        <v>126125237</v>
       </c>
       <c r="B69" t="n">
-        <v>80080</v>
+        <v>82789</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7372,21 +7372,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>600027</v>
+        <v>600038</v>
       </c>
       <c r="R69" t="n">
-        <v>7054254</v>
+        <v>7054626</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7426,12 +7426,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7458,10 +7458,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126125237</v>
+        <v>126125245</v>
       </c>
       <c r="B70" t="n">
-        <v>82789</v>
+        <v>80080</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7469,21 +7469,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>600038</v>
+        <v>600027</v>
       </c>
       <c r="R70" t="n">
-        <v>7054626</v>
+        <v>7054254</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7523,12 +7523,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7749,32 +7749,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126125231</v>
+        <v>126125243</v>
       </c>
       <c r="B73" t="n">
-        <v>91944</v>
+        <v>91242</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7784,10 +7784,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>599886</v>
+        <v>600068</v>
       </c>
       <c r="R73" t="n">
-        <v>7054530</v>
+        <v>7054218</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7814,12 +7814,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7846,32 +7846,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126125243</v>
+        <v>126125231</v>
       </c>
       <c r="B74" t="n">
-        <v>91242</v>
+        <v>91944</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7881,10 +7881,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>600068</v>
+        <v>599886</v>
       </c>
       <c r="R74" t="n">
-        <v>7054218</v>
+        <v>7054530</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -7911,12 +7911,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7946,7 +7946,7 @@
         <v>126125240</v>
       </c>
       <c r="B75" t="n">
-        <v>96475</v>
+        <v>96478</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126125246</v>
+        <v>126125248</v>
       </c>
       <c r="B76" t="n">
-        <v>80080</v>
+        <v>56839</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8051,34 +8051,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>600024</v>
+        <v>600244</v>
       </c>
       <c r="R76" t="n">
-        <v>7054347</v>
+        <v>7054641</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8137,32 +8145,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126125224</v>
+        <v>126125246</v>
       </c>
       <c r="B77" t="n">
-        <v>79984</v>
+        <v>80080</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8172,10 +8180,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>600133</v>
+        <v>600024</v>
       </c>
       <c r="R77" t="n">
-        <v>7054468</v>
+        <v>7054347</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8202,12 +8210,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8234,53 +8242,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126125248</v>
+        <v>126125224</v>
       </c>
       <c r="B78" t="n">
-        <v>56839</v>
+        <v>79984</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>600244</v>
+        <v>600133</v>
       </c>
       <c r="R78" t="n">
-        <v>7054641</v>
+        <v>7054468</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8307,12 +8307,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8436,10 +8436,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126125238</v>
+        <v>126125218</v>
       </c>
       <c r="B80" t="n">
-        <v>80115</v>
+        <v>91207</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8447,21 +8447,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8471,10 +8471,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>600133</v>
+        <v>600128</v>
       </c>
       <c r="R80" t="n">
-        <v>7054468</v>
+        <v>7054464</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8533,10 +8533,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126125218</v>
+        <v>126125238</v>
       </c>
       <c r="B81" t="n">
-        <v>91207</v>
+        <v>80115</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8544,21 +8544,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8568,10 +8568,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>600128</v>
+        <v>600133</v>
       </c>
       <c r="R81" t="n">
-        <v>7054464</v>
+        <v>7054468</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8630,50 +8630,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126125244</v>
+        <v>126125239</v>
       </c>
       <c r="B82" t="n">
-        <v>57656</v>
+        <v>96478</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>600060</v>
+        <v>600142</v>
       </c>
       <c r="R82" t="n">
-        <v>7054259</v>
+        <v>7054514</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8700,17 +8695,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8737,45 +8727,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126125239</v>
+        <v>126125244</v>
       </c>
       <c r="B83" t="n">
-        <v>96475</v>
+        <v>57656</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>600142</v>
+        <v>600060</v>
       </c>
       <c r="R83" t="n">
-        <v>7054514</v>
+        <v>7054259</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8802,12 +8797,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -6368,10 +6368,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126125221</v>
+        <v>126125250</v>
       </c>
       <c r="B59" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6379,42 +6379,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>600131</v>
+        <v>600123</v>
       </c>
       <c r="R59" t="n">
-        <v>7054572</v>
+        <v>7054194</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6441,17 +6433,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6478,10 +6465,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126125235</v>
+        <v>126125221</v>
       </c>
       <c r="B60" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6489,34 +6476,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600140</v>
+        <v>600131</v>
       </c>
       <c r="R60" t="n">
-        <v>7054408</v>
+        <v>7054572</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6549,6 +6544,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6575,32 +6575,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126125230</v>
+        <v>126125235</v>
       </c>
       <c r="B61" t="n">
-        <v>100507</v>
+        <v>91260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1365</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>600150</v>
+        <v>600140</v>
       </c>
       <c r="R61" t="n">
-        <v>7054524</v>
+        <v>7054408</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6672,32 +6672,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126125250</v>
+        <v>126125230</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>100507</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>600123</v>
+        <v>600150</v>
       </c>
       <c r="R62" t="n">
-        <v>7054194</v>
+        <v>7054524</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6737,12 +6737,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7070,32 +7070,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126125247</v>
+        <v>126125242</v>
       </c>
       <c r="B66" t="n">
-        <v>80080</v>
+        <v>96478</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>600058</v>
+        <v>600029</v>
       </c>
       <c r="R66" t="n">
-        <v>7054262</v>
+        <v>7054403</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7135,12 +7135,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7167,32 +7167,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126125242</v>
+        <v>126125247</v>
       </c>
       <c r="B67" t="n">
-        <v>96478</v>
+        <v>80080</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7202,10 +7202,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>600029</v>
+        <v>600058</v>
       </c>
       <c r="R67" t="n">
-        <v>7054403</v>
+        <v>7054262</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7232,12 +7232,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -5490,45 +5490,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126049955</v>
+        <v>126051627</v>
       </c>
       <c r="B50" t="n">
-        <v>91262</v>
+        <v>96478</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599798</v>
+        <v>599926</v>
       </c>
       <c r="R50" t="n">
-        <v>7054459</v>
+        <v>7054220</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5587,45 +5587,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126051627</v>
+        <v>126049955</v>
       </c>
       <c r="B51" t="n">
-        <v>96478</v>
+        <v>91262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599926</v>
+        <v>599798</v>
       </c>
       <c r="R51" t="n">
-        <v>7054220</v>
+        <v>7054459</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5684,45 +5684,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126051924</v>
+        <v>126051767</v>
       </c>
       <c r="B52" t="n">
-        <v>97230</v>
+        <v>57656</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>599973</v>
+        <v>599967</v>
       </c>
       <c r="R52" t="n">
-        <v>7054300</v>
+        <v>7054228</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5755,6 +5760,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5781,27 +5791,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126051822</v>
+        <v>126051924</v>
       </c>
       <c r="B53" t="n">
-        <v>91649</v>
+        <v>97230</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5811,10 +5826,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599974</v>
+        <v>599973</v>
       </c>
       <c r="R53" t="n">
-        <v>7054254</v>
+        <v>7054300</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5873,10 +5888,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126051767</v>
+        <v>126051822</v>
       </c>
       <c r="B54" t="n">
-        <v>57656</v>
+        <v>91649</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5884,39 +5899,29 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599967</v>
+        <v>599974</v>
       </c>
       <c r="R54" t="n">
-        <v>7054228</v>
+        <v>7054254</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5949,11 +5954,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6368,10 +6368,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126125250</v>
+        <v>126125235</v>
       </c>
       <c r="B59" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6379,21 +6379,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6403,10 +6403,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>600123</v>
+        <v>600140</v>
       </c>
       <c r="R59" t="n">
-        <v>7054194</v>
+        <v>7054408</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6433,12 +6433,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6465,10 +6465,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126125221</v>
+        <v>126125250</v>
       </c>
       <c r="B60" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6476,42 +6476,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600131</v>
+        <v>600123</v>
       </c>
       <c r="R60" t="n">
-        <v>7054572</v>
+        <v>7054194</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6538,17 +6530,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6575,32 +6562,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126125235</v>
+        <v>126125230</v>
       </c>
       <c r="B61" t="n">
-        <v>91260</v>
+        <v>100507</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6610,10 +6597,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>600140</v>
+        <v>600150</v>
       </c>
       <c r="R61" t="n">
-        <v>7054408</v>
+        <v>7054524</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6672,45 +6659,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126125230</v>
+        <v>126125221</v>
       </c>
       <c r="B62" t="n">
-        <v>100507</v>
+        <v>57656</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>600150</v>
+        <v>600131</v>
       </c>
       <c r="R62" t="n">
-        <v>7054524</v>
+        <v>7054572</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6743,6 +6738,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7749,32 +7749,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126125243</v>
+        <v>126125231</v>
       </c>
       <c r="B73" t="n">
-        <v>91242</v>
+        <v>91944</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7784,10 +7784,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>600068</v>
+        <v>599886</v>
       </c>
       <c r="R73" t="n">
-        <v>7054218</v>
+        <v>7054530</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7814,12 +7814,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7846,32 +7846,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126125231</v>
+        <v>126125243</v>
       </c>
       <c r="B74" t="n">
-        <v>91944</v>
+        <v>91242</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7881,10 +7881,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>599886</v>
+        <v>600068</v>
       </c>
       <c r="R74" t="n">
-        <v>7054530</v>
+        <v>7054218</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -7911,12 +7911,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -5490,45 +5490,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126051627</v>
+        <v>126049955</v>
       </c>
       <c r="B50" t="n">
-        <v>96478</v>
+        <v>91262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599926</v>
+        <v>599798</v>
       </c>
       <c r="R50" t="n">
-        <v>7054220</v>
+        <v>7054459</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5587,45 +5587,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126049955</v>
+        <v>126051627</v>
       </c>
       <c r="B51" t="n">
-        <v>91262</v>
+        <v>96478</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599798</v>
+        <v>599926</v>
       </c>
       <c r="R51" t="n">
-        <v>7054459</v>
+        <v>7054220</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -8040,53 +8040,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126125248</v>
+        <v>126125224</v>
       </c>
       <c r="B76" t="n">
-        <v>56839</v>
+        <v>79984</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>600244</v>
+        <v>600133</v>
       </c>
       <c r="R76" t="n">
-        <v>7054641</v>
+        <v>7054468</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8113,12 +8105,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8242,45 +8234,53 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126125224</v>
+        <v>126125248</v>
       </c>
       <c r="B78" t="n">
-        <v>79984</v>
+        <v>56839</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6456</v>
+        <v>102612</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>600133</v>
+        <v>600244</v>
       </c>
       <c r="R78" t="n">
-        <v>7054468</v>
+        <v>7054641</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8307,12 +8307,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -3998,7 +3998,7 @@
         <v>126049680</v>
       </c>
       <c r="B35" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>126051874</v>
       </c>
       <c r="B36" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>126050156</v>
       </c>
       <c r="B37" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>126049400</v>
       </c>
       <c r="B38" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>126050308</v>
       </c>
       <c r="B39" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>126051995</v>
       </c>
       <c r="B40" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>126051788</v>
       </c>
       <c r="B41" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>126049913</v>
       </c>
       <c r="B42" t="n">
-        <v>80108</v>
+        <v>80111</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>126050100</v>
       </c>
       <c r="B43" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>126048270</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4985,45 +4985,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126049595</v>
+        <v>126050300</v>
       </c>
       <c r="B45" t="n">
-        <v>75072</v>
+        <v>91699</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599888</v>
+        <v>599845</v>
       </c>
       <c r="R45" t="n">
-        <v>7054532</v>
+        <v>7054329</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5082,45 +5082,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126050300</v>
+        <v>126049595</v>
       </c>
       <c r="B46" t="n">
-        <v>91696</v>
+        <v>75075</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599845</v>
+        <v>599888</v>
       </c>
       <c r="R46" t="n">
-        <v>7054329</v>
+        <v>7054532</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5182,7 +5182,7 @@
         <v>126050019</v>
       </c>
       <c r="B47" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>126050066</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>126051739</v>
       </c>
       <c r="B49" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>126049955</v>
       </c>
       <c r="B50" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>126051627</v>
       </c>
       <c r="B51" t="n">
-        <v>96478</v>
+        <v>96487</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>126051767</v>
       </c>
       <c r="B52" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5791,32 +5791,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126051924</v>
+        <v>126051822</v>
       </c>
       <c r="B53" t="n">
-        <v>97230</v>
+        <v>91652</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5826,10 +5821,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599973</v>
+        <v>599974</v>
       </c>
       <c r="R53" t="n">
-        <v>7054300</v>
+        <v>7054254</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5888,27 +5883,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126051822</v>
+        <v>126051924</v>
       </c>
       <c r="B54" t="n">
-        <v>91649</v>
+        <v>97239</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599974</v>
+        <v>599973</v>
       </c>
       <c r="R54" t="n">
-        <v>7054254</v>
+        <v>7054300</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5983,7 +5983,7 @@
         <v>126125252</v>
       </c>
       <c r="B55" t="n">
-        <v>96478</v>
+        <v>96487</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>126125225</v>
       </c>
       <c r="B56" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>126125232</v>
       </c>
       <c r="B57" t="n">
-        <v>91944</v>
+        <v>91947</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>126125220</v>
       </c>
       <c r="B58" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>126125235</v>
       </c>
       <c r="B59" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>126125250</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>126125230</v>
       </c>
       <c r="B61" t="n">
-        <v>100507</v>
+        <v>100516</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>126125221</v>
       </c>
       <c r="B62" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>126125249</v>
       </c>
       <c r="B63" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>126125222</v>
       </c>
       <c r="B64" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>126125223</v>
       </c>
       <c r="B65" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>126125242</v>
       </c>
       <c r="B66" t="n">
-        <v>96478</v>
+        <v>96487</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>126125247</v>
       </c>
       <c r="B67" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>126125227</v>
       </c>
       <c r="B68" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7361,10 +7361,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126125237</v>
+        <v>126125245</v>
       </c>
       <c r="B69" t="n">
-        <v>82789</v>
+        <v>80083</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7372,21 +7372,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>600038</v>
+        <v>600027</v>
       </c>
       <c r="R69" t="n">
-        <v>7054626</v>
+        <v>7054254</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7426,12 +7426,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7458,10 +7458,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126125245</v>
+        <v>126125237</v>
       </c>
       <c r="B70" t="n">
-        <v>80080</v>
+        <v>82792</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7469,21 +7469,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>600027</v>
+        <v>600038</v>
       </c>
       <c r="R70" t="n">
-        <v>7054254</v>
+        <v>7054626</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7523,12 +7523,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7558,7 +7558,7 @@
         <v>126125228</v>
       </c>
       <c r="B71" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>126125216</v>
       </c>
       <c r="B72" t="n">
-        <v>91417</v>
+        <v>91420</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>126125231</v>
       </c>
       <c r="B73" t="n">
-        <v>91944</v>
+        <v>91947</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>126125243</v>
       </c>
       <c r="B74" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>126125240</v>
       </c>
       <c r="B75" t="n">
-        <v>96478</v>
+        <v>96487</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8040,32 +8040,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126125224</v>
+        <v>126125246</v>
       </c>
       <c r="B76" t="n">
-        <v>79984</v>
+        <v>80083</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>600133</v>
+        <v>600024</v>
       </c>
       <c r="R76" t="n">
-        <v>7054468</v>
+        <v>7054347</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8105,12 +8105,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8137,32 +8137,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126125246</v>
+        <v>126125224</v>
       </c>
       <c r="B77" t="n">
-        <v>80080</v>
+        <v>79987</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8172,10 +8172,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>600024</v>
+        <v>600133</v>
       </c>
       <c r="R77" t="n">
-        <v>7054347</v>
+        <v>7054468</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8202,12 +8202,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8237,7 +8237,7 @@
         <v>126125248</v>
       </c>
       <c r="B78" t="n">
-        <v>56839</v>
+        <v>56840</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>126125229</v>
       </c>
       <c r="B79" t="n">
-        <v>80116</v>
+        <v>80119</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>126125218</v>
       </c>
       <c r="B80" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>126125238</v>
       </c>
       <c r="B81" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>126125239</v>
       </c>
       <c r="B82" t="n">
-        <v>96478</v>
+        <v>96487</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>126125244</v>
       </c>
       <c r="B83" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>126125217</v>
       </c>
       <c r="B84" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -4985,45 +4985,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126050300</v>
+        <v>126049595</v>
       </c>
       <c r="B45" t="n">
-        <v>91699</v>
+        <v>75075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599845</v>
+        <v>599888</v>
       </c>
       <c r="R45" t="n">
-        <v>7054329</v>
+        <v>7054532</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5082,45 +5082,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126049595</v>
+        <v>126050300</v>
       </c>
       <c r="B46" t="n">
-        <v>75075</v>
+        <v>91699</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599888</v>
+        <v>599845</v>
       </c>
       <c r="R46" t="n">
-        <v>7054532</v>
+        <v>7054329</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5490,45 +5490,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126049955</v>
+        <v>126051627</v>
       </c>
       <c r="B50" t="n">
-        <v>91265</v>
+        <v>96487</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599798</v>
+        <v>599926</v>
       </c>
       <c r="R50" t="n">
-        <v>7054459</v>
+        <v>7054220</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5587,45 +5587,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126051627</v>
+        <v>126049955</v>
       </c>
       <c r="B51" t="n">
-        <v>96487</v>
+        <v>91265</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599926</v>
+        <v>599798</v>
       </c>
       <c r="R51" t="n">
-        <v>7054220</v>
+        <v>7054459</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5791,27 +5791,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126051822</v>
+        <v>126051924</v>
       </c>
       <c r="B53" t="n">
-        <v>91652</v>
+        <v>97239</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5821,10 +5826,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599974</v>
+        <v>599973</v>
       </c>
       <c r="R53" t="n">
-        <v>7054254</v>
+        <v>7054300</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5883,32 +5888,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126051924</v>
+        <v>126051822</v>
       </c>
       <c r="B54" t="n">
-        <v>97239</v>
+        <v>91652</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599973</v>
+        <v>599974</v>
       </c>
       <c r="R54" t="n">
-        <v>7054300</v>
+        <v>7054254</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -4490,10 +4490,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126051995</v>
+        <v>126051788</v>
       </c>
       <c r="B40" t="n">
-        <v>91263</v>
+        <v>80083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4501,21 +4501,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599997</v>
+        <v>599973</v>
       </c>
       <c r="R40" t="n">
-        <v>7054327</v>
+        <v>7054239</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126051788</v>
+        <v>126051995</v>
       </c>
       <c r="B41" t="n">
-        <v>80083</v>
+        <v>91263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599973</v>
+        <v>599997</v>
       </c>
       <c r="R41" t="n">
-        <v>7054239</v>
+        <v>7054327</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5286,10 +5286,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126050066</v>
+        <v>126051739</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5297,34 +5297,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Antemyrorna, Antemyrorna, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599854</v>
+        <v>599977</v>
       </c>
       <c r="R48" t="n">
-        <v>7054375</v>
+        <v>7054216</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5357,6 +5362,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5383,10 +5393,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126051739</v>
+        <v>126050066</v>
       </c>
       <c r="B49" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5394,39 +5404,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Antemyrorna, Antemyrorna, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599977</v>
+        <v>599854</v>
       </c>
       <c r="R49" t="n">
-        <v>7054216</v>
+        <v>7054375</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5459,11 +5464,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5791,32 +5791,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126051924</v>
+        <v>126051822</v>
       </c>
       <c r="B53" t="n">
-        <v>97239</v>
+        <v>91652</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5826,10 +5821,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599973</v>
+        <v>599974</v>
       </c>
       <c r="R53" t="n">
-        <v>7054300</v>
+        <v>7054254</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5888,27 +5883,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126051822</v>
+        <v>126051924</v>
       </c>
       <c r="B54" t="n">
-        <v>91652</v>
+        <v>97239</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599974</v>
+        <v>599973</v>
       </c>
       <c r="R54" t="n">
-        <v>7054254</v>
+        <v>7054300</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6368,10 +6368,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126125235</v>
+        <v>126125221</v>
       </c>
       <c r="B59" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6379,34 +6379,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>600140</v>
+        <v>600131</v>
       </c>
       <c r="R59" t="n">
-        <v>7054408</v>
+        <v>7054572</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6439,6 +6447,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6465,10 +6478,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126125250</v>
+        <v>126125235</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>91263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6476,21 +6489,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6500,10 +6513,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600123</v>
+        <v>600140</v>
       </c>
       <c r="R60" t="n">
-        <v>7054194</v>
+        <v>7054408</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6530,12 +6543,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6659,10 +6672,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126125221</v>
+        <v>126125250</v>
       </c>
       <c r="B62" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6670,42 +6683,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>600131</v>
+        <v>600123</v>
       </c>
       <c r="R62" t="n">
-        <v>7054572</v>
+        <v>7054194</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6732,17 +6737,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7070,32 +7070,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126125242</v>
+        <v>126125247</v>
       </c>
       <c r="B66" t="n">
-        <v>96487</v>
+        <v>80083</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>600029</v>
+        <v>600058</v>
       </c>
       <c r="R66" t="n">
-        <v>7054403</v>
+        <v>7054262</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7135,12 +7135,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7167,32 +7167,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126125247</v>
+        <v>126125242</v>
       </c>
       <c r="B67" t="n">
-        <v>80083</v>
+        <v>96487</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7202,10 +7202,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>600058</v>
+        <v>600029</v>
       </c>
       <c r="R67" t="n">
-        <v>7054262</v>
+        <v>7054403</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7232,12 +7232,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7361,10 +7361,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126125245</v>
+        <v>126125237</v>
       </c>
       <c r="B69" t="n">
-        <v>80083</v>
+        <v>82792</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7372,21 +7372,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>600027</v>
+        <v>600038</v>
       </c>
       <c r="R69" t="n">
-        <v>7054254</v>
+        <v>7054626</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7426,12 +7426,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7458,10 +7458,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126125237</v>
+        <v>126125245</v>
       </c>
       <c r="B70" t="n">
-        <v>82792</v>
+        <v>80083</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7469,21 +7469,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>600038</v>
+        <v>600027</v>
       </c>
       <c r="R70" t="n">
-        <v>7054626</v>
+        <v>7054254</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7523,12 +7523,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8040,10 +8040,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126125246</v>
+        <v>126125248</v>
       </c>
       <c r="B76" t="n">
-        <v>80083</v>
+        <v>56840</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8051,34 +8051,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>600024</v>
+        <v>600244</v>
       </c>
       <c r="R76" t="n">
-        <v>7054347</v>
+        <v>7054641</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8137,32 +8145,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126125224</v>
+        <v>126125246</v>
       </c>
       <c r="B77" t="n">
-        <v>79987</v>
+        <v>80083</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8172,10 +8180,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>600133</v>
+        <v>600024</v>
       </c>
       <c r="R77" t="n">
-        <v>7054468</v>
+        <v>7054347</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8202,12 +8210,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8234,53 +8242,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126125248</v>
+        <v>126125224</v>
       </c>
       <c r="B78" t="n">
-        <v>56840</v>
+        <v>79987</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>600244</v>
+        <v>600133</v>
       </c>
       <c r="R78" t="n">
-        <v>7054641</v>
+        <v>7054468</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8307,12 +8307,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8436,10 +8436,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126125218</v>
+        <v>126125238</v>
       </c>
       <c r="B80" t="n">
-        <v>91210</v>
+        <v>80118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8447,21 +8447,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8471,10 +8471,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>600128</v>
+        <v>600133</v>
       </c>
       <c r="R80" t="n">
-        <v>7054464</v>
+        <v>7054468</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8533,10 +8533,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126125238</v>
+        <v>126125218</v>
       </c>
       <c r="B81" t="n">
-        <v>80118</v>
+        <v>91210</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8544,21 +8544,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8568,10 +8568,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>600133</v>
+        <v>600128</v>
       </c>
       <c r="R81" t="n">
-        <v>7054468</v>
+        <v>7054464</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8630,45 +8630,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126125239</v>
+        <v>126125244</v>
       </c>
       <c r="B82" t="n">
-        <v>96487</v>
+        <v>57657</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>600142</v>
+        <v>600060</v>
       </c>
       <c r="R82" t="n">
-        <v>7054514</v>
+        <v>7054259</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8695,12 +8700,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8727,50 +8737,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126125244</v>
+        <v>126125239</v>
       </c>
       <c r="B83" t="n">
-        <v>57657</v>
+        <v>96487</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>600060</v>
+        <v>600142</v>
       </c>
       <c r="R83" t="n">
-        <v>7054259</v>
+        <v>7054514</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8797,17 +8802,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -5490,45 +5490,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126051627</v>
+        <v>126049955</v>
       </c>
       <c r="B50" t="n">
-        <v>96487</v>
+        <v>91265</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599926</v>
+        <v>599798</v>
       </c>
       <c r="R50" t="n">
-        <v>7054220</v>
+        <v>7054459</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5587,45 +5587,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126049955</v>
+        <v>126051627</v>
       </c>
       <c r="B51" t="n">
-        <v>91265</v>
+        <v>96487</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599798</v>
+        <v>599926</v>
       </c>
       <c r="R51" t="n">
-        <v>7054459</v>
+        <v>7054220</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5684,50 +5684,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126051767</v>
+        <v>126051924</v>
       </c>
       <c r="B52" t="n">
-        <v>57657</v>
+        <v>97239</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>599967</v>
+        <v>599973</v>
       </c>
       <c r="R52" t="n">
-        <v>7054228</v>
+        <v>7054300</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5760,11 +5755,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5883,45 +5873,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126051924</v>
+        <v>126051767</v>
       </c>
       <c r="B54" t="n">
-        <v>97239</v>
+        <v>57657</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599973</v>
+        <v>599967</v>
       </c>
       <c r="R54" t="n">
-        <v>7054300</v>
+        <v>7054228</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5954,6 +5949,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6368,53 +6368,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126125221</v>
+        <v>126125230</v>
       </c>
       <c r="B59" t="n">
-        <v>57657</v>
+        <v>100516</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>600131</v>
+        <v>600150</v>
       </c>
       <c r="R59" t="n">
-        <v>7054572</v>
+        <v>7054524</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6447,11 +6439,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6478,10 +6465,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126125235</v>
+        <v>126125250</v>
       </c>
       <c r="B60" t="n">
-        <v>91263</v>
+        <v>78980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6489,21 +6476,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6513,10 +6500,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600140</v>
+        <v>600123</v>
       </c>
       <c r="R60" t="n">
-        <v>7054408</v>
+        <v>7054194</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6543,12 +6530,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6575,45 +6562,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126125230</v>
+        <v>126125221</v>
       </c>
       <c r="B61" t="n">
-        <v>100516</v>
+        <v>57657</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>600150</v>
+        <v>600131</v>
       </c>
       <c r="R61" t="n">
-        <v>7054524</v>
+        <v>7054572</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6646,6 +6641,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6672,10 +6672,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126125250</v>
+        <v>126125235</v>
       </c>
       <c r="B62" t="n">
-        <v>78980</v>
+        <v>91263</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6683,21 +6683,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>600123</v>
+        <v>600140</v>
       </c>
       <c r="R62" t="n">
-        <v>7054194</v>
+        <v>7054408</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6737,12 +6737,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8040,10 +8040,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126125248</v>
+        <v>126125246</v>
       </c>
       <c r="B76" t="n">
-        <v>56840</v>
+        <v>80083</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8051,42 +8051,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>600244</v>
+        <v>600024</v>
       </c>
       <c r="R76" t="n">
-        <v>7054641</v>
+        <v>7054347</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8145,32 +8137,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126125246</v>
+        <v>126125224</v>
       </c>
       <c r="B77" t="n">
-        <v>80083</v>
+        <v>79987</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8180,10 +8172,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>600024</v>
+        <v>600133</v>
       </c>
       <c r="R77" t="n">
-        <v>7054347</v>
+        <v>7054468</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8210,12 +8202,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8242,45 +8234,53 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126125224</v>
+        <v>126125248</v>
       </c>
       <c r="B78" t="n">
-        <v>79987</v>
+        <v>56840</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6456</v>
+        <v>102612</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>600133</v>
+        <v>600244</v>
       </c>
       <c r="R78" t="n">
-        <v>7054468</v>
+        <v>7054641</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8307,12 +8307,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8436,10 +8436,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126125238</v>
+        <v>126125218</v>
       </c>
       <c r="B80" t="n">
-        <v>80118</v>
+        <v>91210</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8447,21 +8447,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8471,10 +8471,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>600133</v>
+        <v>600128</v>
       </c>
       <c r="R80" t="n">
-        <v>7054468</v>
+        <v>7054464</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8533,10 +8533,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126125218</v>
+        <v>126125238</v>
       </c>
       <c r="B81" t="n">
-        <v>91210</v>
+        <v>80118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8544,21 +8544,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8568,10 +8568,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>600128</v>
+        <v>600133</v>
       </c>
       <c r="R81" t="n">
-        <v>7054464</v>
+        <v>7054468</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -5490,45 +5490,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126049955</v>
+        <v>126051627</v>
       </c>
       <c r="B50" t="n">
-        <v>91265</v>
+        <v>96487</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599798</v>
+        <v>599926</v>
       </c>
       <c r="R50" t="n">
-        <v>7054459</v>
+        <v>7054220</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5587,45 +5587,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126051627</v>
+        <v>126049955</v>
       </c>
       <c r="B51" t="n">
-        <v>96487</v>
+        <v>91265</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599926</v>
+        <v>599798</v>
       </c>
       <c r="R51" t="n">
-        <v>7054220</v>
+        <v>7054459</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -8436,10 +8436,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126125218</v>
+        <v>126125238</v>
       </c>
       <c r="B80" t="n">
-        <v>91210</v>
+        <v>80118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8447,21 +8447,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8471,10 +8471,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>600128</v>
+        <v>600133</v>
       </c>
       <c r="R80" t="n">
-        <v>7054464</v>
+        <v>7054468</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8533,10 +8533,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126125238</v>
+        <v>126125218</v>
       </c>
       <c r="B81" t="n">
-        <v>80118</v>
+        <v>91210</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8544,21 +8544,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8568,10 +8568,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>600133</v>
+        <v>600128</v>
       </c>
       <c r="R81" t="n">
-        <v>7054468</v>
+        <v>7054464</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>

--- a/artfynd/A 22516-2025 artfynd.xlsx
+++ b/artfynd/A 22516-2025 artfynd.xlsx
@@ -5286,10 +5286,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126051739</v>
+        <v>126050066</v>
       </c>
       <c r="B48" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5297,39 +5297,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+          <t>Antemyrorna, Antemyrorna, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599977</v>
+        <v>599854</v>
       </c>
       <c r="R48" t="n">
-        <v>7054216</v>
+        <v>7054375</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5362,11 +5357,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5393,10 +5383,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126050066</v>
+        <v>126051739</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5404,34 +5394,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Antemyrorna, Antemyrorna, Ång</t>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599854</v>
+        <v>599977</v>
       </c>
       <c r="R49" t="n">
-        <v>7054375</v>
+        <v>7054216</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5464,6 +5459,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5684,45 +5684,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126051924</v>
+        <v>126051767</v>
       </c>
       <c r="B52" t="n">
-        <v>97239</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>599973</v>
+        <v>599967</v>
       </c>
       <c r="R52" t="n">
-        <v>7054300</v>
+        <v>7054228</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5755,6 +5760,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5873,50 +5883,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126051767</v>
+        <v>126051924</v>
       </c>
       <c r="B54" t="n">
-        <v>57657</v>
+        <v>97239</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599967</v>
+        <v>599973</v>
       </c>
       <c r="R54" t="n">
-        <v>7054228</v>
+        <v>7054300</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5949,11 +5954,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6368,45 +6368,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126125230</v>
+        <v>126125221</v>
       </c>
       <c r="B59" t="n">
-        <v>100516</v>
+        <v>57657</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>600150</v>
+        <v>600131</v>
       </c>
       <c r="R59" t="n">
-        <v>7054524</v>
+        <v>7054572</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6439,6 +6447,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6465,10 +6478,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126125250</v>
+        <v>126125235</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>91263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6476,21 +6489,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6500,10 +6513,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600123</v>
+        <v>600140</v>
       </c>
       <c r="R60" t="n">
-        <v>7054194</v>
+        <v>7054408</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6530,12 +6543,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6562,53 +6575,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126125221</v>
+        <v>126125230</v>
       </c>
       <c r="B61" t="n">
-        <v>57657</v>
+        <v>100516</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>600131</v>
+        <v>600150</v>
       </c>
       <c r="R61" t="n">
-        <v>7054572</v>
+        <v>7054524</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6641,11 +6646,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Några år gammalt bohål, 1.5m upp. 4-4.5 cm diameter + granticka</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6672,10 +6672,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126125235</v>
+        <v>126125250</v>
       </c>
       <c r="B62" t="n">
-        <v>91263</v>
+        <v>78980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6683,21 +6683,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>600140</v>
+        <v>600123</v>
       </c>
       <c r="R62" t="n">
-        <v>7054408</v>
+        <v>7054194</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6737,12 +6737,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7070,32 +7070,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126125247</v>
+        <v>126125242</v>
       </c>
       <c r="B66" t="n">
-        <v>80083</v>
+        <v>96487</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>600058</v>
+        <v>600029</v>
       </c>
       <c r="R66" t="n">
-        <v>7054262</v>
+        <v>7054403</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7135,12 +7135,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7167,32 +7167,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126125242</v>
+        <v>126125247</v>
       </c>
       <c r="B67" t="n">
-        <v>96487</v>
+        <v>80083</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7202,10 +7202,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>600029</v>
+        <v>600058</v>
       </c>
       <c r="R67" t="n">
-        <v>7054403</v>
+        <v>7054262</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7232,12 +7232,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8040,10 +8040,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126125246</v>
+        <v>126125248</v>
       </c>
       <c r="B76" t="n">
-        <v>80083</v>
+        <v>56840</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8051,34 +8051,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>600024</v>
+        <v>600244</v>
       </c>
       <c r="R76" t="n">
-        <v>7054347</v>
+        <v>7054641</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8137,32 +8145,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126125224</v>
+        <v>126125246</v>
       </c>
       <c r="B77" t="n">
-        <v>79987</v>
+        <v>80083</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8172,10 +8180,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>600133</v>
+        <v>600024</v>
       </c>
       <c r="R77" t="n">
-        <v>7054468</v>
+        <v>7054347</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8202,12 +8210,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8234,53 +8242,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126125248</v>
+        <v>126125224</v>
       </c>
       <c r="B78" t="n">
-        <v>56840</v>
+        <v>79987</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>600244</v>
+        <v>600133</v>
       </c>
       <c r="R78" t="n">
-        <v>7054641</v>
+        <v>7054468</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8307,12 +8307,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
